--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0004_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0004_ses-01_WMprob_pdf.xlsx
@@ -1,6 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
@@ -56,16 +57,16 @@
   <dimension ref="A1:L100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="true"/>
+    <col min="1" max="1" width="14.7109375" customWidth="true"/>
     <col min="2" max="2" width="13.7109375" customWidth="true"/>
     <col min="3" max="3" width="14.7109375" customWidth="true"/>
-    <col min="4" max="4" width="14.7109375" customWidth="true"/>
-    <col min="5" max="5" width="15.7109375" customWidth="true"/>
+    <col min="4" max="4" width="13.7109375" customWidth="true"/>
+    <col min="5" max="5" width="14.7109375" customWidth="true"/>
     <col min="6" max="6" width="14.7109375" customWidth="true"/>
     <col min="7" max="7" width="13.7109375" customWidth="true"/>
     <col min="8" max="8" width="14.7109375" customWidth="true"/>
     <col min="9" max="9" width="14.7109375" customWidth="true"/>
-    <col min="10" max="10" width="13.7109375" customWidth="true"/>
+    <col min="10" max="10" width="12.7109375" customWidth="true"/>
     <col min="11" max="11" width="12.7109375" customWidth="true"/>
     <col min="12" max="12" width="14.7109375" customWidth="true"/>
   </cols>
@@ -540,7 +541,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="0">
-        <v>0.0005966765118291113</v>
+        <v>0</v>
       </c>
       <c r="F13" s="0">
         <v>0</v>
@@ -616,7 +617,7 @@
         <v>0</v>
       </c>
       <c r="E15" s="0">
-        <v>0.0029833825591455651</v>
+        <v>0</v>
       </c>
       <c r="F15" s="0">
         <v>0</v>
@@ -654,7 +655,7 @@
         <v>0</v>
       </c>
       <c r="E16" s="0">
-        <v>0.0047734120946328904</v>
+        <v>0</v>
       </c>
       <c r="F16" s="0">
         <v>0</v>
@@ -675,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="0">
-        <v>0.0015550648462040854</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -686,13 +687,13 @@
         <v>0</v>
       </c>
       <c r="C17" s="0">
-        <v>0.001268086077682952</v>
+        <v>0</v>
       </c>
       <c r="D17" s="0">
         <v>0</v>
       </c>
       <c r="E17" s="0">
-        <v>0.016706942331215117</v>
+        <v>0</v>
       </c>
       <c r="F17" s="0">
         <v>0</v>
@@ -713,36 +714,36 @@
         <v>0</v>
       </c>
       <c r="L17" s="0">
-        <v>0.0046651945386122556</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="0">
-        <v>0.0024613566998129416</v>
+        <v>0</v>
       </c>
       <c r="B18" s="0">
         <v>0</v>
       </c>
       <c r="C18" s="0">
-        <v>0.0012680860776829556</v>
+        <v>0</v>
       </c>
       <c r="D18" s="0">
-        <v>0.0024042507152645925</v>
+        <v>0</v>
       </c>
       <c r="E18" s="0">
-        <v>0.041767355828037908</v>
+        <v>0</v>
       </c>
       <c r="F18" s="0">
-        <v>0.0054579194411090593</v>
+        <v>0</v>
       </c>
       <c r="G18" s="0">
         <v>0</v>
       </c>
       <c r="H18" s="0">
-        <v>0.0056808498551383394</v>
+        <v>0</v>
       </c>
       <c r="I18" s="0">
-        <v>0.0019860578737264439</v>
+        <v>0</v>
       </c>
       <c r="J18" s="0">
         <v>0</v>
@@ -751,36 +752,36 @@
         <v>0</v>
       </c>
       <c r="L18" s="0">
-        <v>0.0046651945386122686</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="0">
-        <v>0.024613566998129346</v>
+        <v>0</v>
       </c>
       <c r="B19" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C19" s="0">
-        <v>0.0038042582330488559</v>
+        <v>0</v>
       </c>
       <c r="D19" s="0">
-        <v>0.019234005722116688</v>
+        <v>0</v>
       </c>
       <c r="E19" s="0">
-        <v>0.096661594916316027</v>
+        <v>0</v>
       </c>
       <c r="F19" s="0">
-        <v>0.0072772259214787249</v>
+        <v>0</v>
       </c>
       <c r="G19" s="0">
-        <v>0.020116676725005011</v>
+        <v>0</v>
       </c>
       <c r="H19" s="0">
         <v>0</v>
       </c>
       <c r="I19" s="0">
-        <v>0.0099302893686321926</v>
+        <v>0</v>
       </c>
       <c r="J19" s="0">
         <v>0</v>
@@ -789,36 +790,36 @@
         <v>0</v>
       </c>
       <c r="L19" s="0">
-        <v>0.010885453923428597</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="0">
-        <v>0.051688490696071628</v>
+        <v>0</v>
       </c>
       <c r="B20" s="0">
-        <v>0.087719298245613961</v>
+        <v>0</v>
       </c>
       <c r="C20" s="0">
-        <v>0.016485119009878375</v>
+        <v>0</v>
       </c>
       <c r="D20" s="0">
-        <v>0.045680763590027124</v>
+        <v>0</v>
       </c>
       <c r="E20" s="0">
-        <v>0.21361019123482186</v>
+        <v>0</v>
       </c>
       <c r="F20" s="0">
-        <v>0.0291089036859149</v>
+        <v>0</v>
       </c>
       <c r="G20" s="0">
-        <v>0.040233353450010022</v>
+        <v>0</v>
       </c>
       <c r="H20" s="0">
-        <v>0.022723399420553292</v>
+        <v>0</v>
       </c>
       <c r="I20" s="0">
-        <v>0.011916347242358632</v>
+        <v>0</v>
       </c>
       <c r="J20" s="0">
         <v>0</v>
@@ -827,3047 +828,3047 @@
         <v>0</v>
       </c>
       <c r="L20" s="0">
-        <v>0.037321556308898045</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="0">
-        <v>0.13045190509008589</v>
+        <v>0</v>
       </c>
       <c r="B21" s="0">
-        <v>0.087719298245614197</v>
+        <v>0</v>
       </c>
       <c r="C21" s="0">
-        <v>0.032970238019756841</v>
+        <v>0</v>
       </c>
       <c r="D21" s="0">
-        <v>0.10097853004111287</v>
+        <v>0</v>
       </c>
       <c r="E21" s="0">
-        <v>0.46421432620304987</v>
+        <v>0</v>
       </c>
       <c r="F21" s="0">
-        <v>0.063675726812939024</v>
+        <v>0</v>
       </c>
       <c r="G21" s="0">
-        <v>0.10058338362502532</v>
+        <v>0</v>
       </c>
       <c r="H21" s="0">
-        <v>0.06817019826166007</v>
+        <v>0</v>
       </c>
       <c r="I21" s="0">
-        <v>0.027804810232170216</v>
+        <v>0</v>
       </c>
       <c r="J21" s="0">
         <v>0</v>
       </c>
       <c r="K21" s="0">
-        <v>0.12886597938144354</v>
+        <v>0</v>
       </c>
       <c r="L21" s="0">
-        <v>0.090193761079837204</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="0">
-        <v>0.33720586787437201</v>
+        <v>0</v>
       </c>
       <c r="B22" s="0">
-        <v>0.61403508771929771</v>
+        <v>0</v>
       </c>
       <c r="C22" s="0">
-        <v>0.1268086077682952</v>
+        <v>0</v>
       </c>
       <c r="D22" s="0">
-        <v>0.2548505758180461</v>
+        <v>0</v>
       </c>
       <c r="E22" s="0">
-        <v>0.84847399982099636</v>
+        <v>0</v>
       </c>
       <c r="F22" s="0">
-        <v>0.21831677764436178</v>
+        <v>0</v>
       </c>
       <c r="G22" s="0">
-        <v>0.16093341380004009</v>
+        <v>0</v>
       </c>
       <c r="H22" s="0">
-        <v>0.14202124637845809</v>
+        <v>0</v>
       </c>
       <c r="I22" s="0">
-        <v>0.087386546443963306</v>
+        <v>0</v>
       </c>
       <c r="J22" s="0">
-        <v>0.092013249907986677</v>
+        <v>0</v>
       </c>
       <c r="K22" s="0">
-        <v>0.64432989690721587</v>
+        <v>0</v>
       </c>
       <c r="L22" s="0">
-        <v>0.22548440269959236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="0">
-        <v>0.64241409865117594</v>
+        <v>0</v>
       </c>
       <c r="B23" s="0">
-        <v>0.70175438596491169</v>
+        <v>0</v>
       </c>
       <c r="C23" s="0">
-        <v>0.29165979786707896</v>
+        <v>0</v>
       </c>
       <c r="D23" s="0">
-        <v>0.48325439376818174</v>
+        <v>0</v>
       </c>
       <c r="E23" s="0">
-        <v>1.2750977057788109</v>
+        <v>0</v>
       </c>
       <c r="F23" s="0">
-        <v>0.38205436087763311</v>
+        <v>0</v>
       </c>
       <c r="G23" s="0">
-        <v>0.38221685777509523</v>
+        <v>0</v>
       </c>
       <c r="H23" s="0">
-        <v>0.44310628870078922</v>
+        <v>0</v>
       </c>
       <c r="I23" s="0">
-        <v>0.25222934996325769</v>
+        <v>0</v>
       </c>
       <c r="J23" s="0">
-        <v>0.331247699668752</v>
+        <v>0</v>
       </c>
       <c r="K23" s="0">
-        <v>0.64432989690721587</v>
+        <v>0</v>
       </c>
       <c r="L23" s="0">
-        <v>0.43697322178334796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="0">
-        <v>1.1026878015161978</v>
+        <v>0</v>
       </c>
       <c r="B24" s="0">
-        <v>1.4035087719298271</v>
+        <v>0</v>
       </c>
       <c r="C24" s="0">
-        <v>0.54020466909293907</v>
+        <v>0</v>
       </c>
       <c r="D24" s="0">
-        <v>1.1684658476185918</v>
+        <v>0</v>
       </c>
       <c r="E24" s="0">
-        <v>1.9338285748381554</v>
+        <v>0</v>
       </c>
       <c r="F24" s="0">
-        <v>0.84597751337190419</v>
+        <v>0</v>
       </c>
       <c r="G24" s="0">
-        <v>0.74431703882518752</v>
+        <v>0</v>
       </c>
       <c r="H24" s="0">
-        <v>0.69874453218201571</v>
+        <v>0</v>
       </c>
       <c r="I24" s="0">
-        <v>0.5163750471688755</v>
+        <v>0</v>
       </c>
       <c r="J24" s="0">
-        <v>0.66249539933750579</v>
+        <v>0</v>
       </c>
       <c r="K24" s="0">
-        <v>2.1907216494845398</v>
+        <v>0</v>
       </c>
       <c r="L24" s="0">
-        <v>0.83973501695020836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="0">
-        <v>1.816481244461946</v>
+        <v>0</v>
       </c>
       <c r="B25" s="0">
-        <v>2.368421052631577</v>
+        <v>0</v>
       </c>
       <c r="C25" s="0">
-        <v>1.053779530554533</v>
+        <v>0</v>
       </c>
       <c r="D25" s="0">
-        <v>1.8007837857331748</v>
+        <v>0</v>
       </c>
       <c r="E25" s="0">
-        <v>2.6993645395148995</v>
+        <v>0</v>
       </c>
       <c r="F25" s="0">
-        <v>1.3644798602772612</v>
+        <v>0</v>
       </c>
       <c r="G25" s="0">
-        <v>1.0058338362502506</v>
+        <v>0</v>
       </c>
       <c r="H25" s="0">
-        <v>1.1986593194341861</v>
+        <v>0</v>
       </c>
       <c r="I25" s="0">
-        <v>1.0109034577267573</v>
+        <v>0</v>
       </c>
       <c r="J25" s="0">
-        <v>1.0489510489510481</v>
+        <v>0</v>
       </c>
       <c r="K25" s="0">
-        <v>3.3505154639175228</v>
+        <v>0</v>
       </c>
       <c r="L25" s="0">
-        <v>1.3762323888906156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="0">
-        <v>2.6484198089987179</v>
+        <v>0</v>
       </c>
       <c r="B26" s="0">
-        <v>4.4736842105263115</v>
+        <v>0</v>
       </c>
       <c r="C26" s="0">
-        <v>1.6421714705994228</v>
+        <v>0</v>
       </c>
       <c r="D26" s="0">
-        <v>2.8610583511648566</v>
+        <v>0</v>
       </c>
       <c r="E26" s="0">
-        <v>3.2029595154986699</v>
+        <v>0</v>
       </c>
       <c r="F26" s="0">
-        <v>2.1413237273951151</v>
+        <v>0</v>
       </c>
       <c r="G26" s="0">
-        <v>2.0317843492255059</v>
+        <v>0</v>
       </c>
       <c r="H26" s="0">
-        <v>1.9598932000227216</v>
+        <v>0</v>
       </c>
       <c r="I26" s="0">
-        <v>1.6047347619709624</v>
+        <v>0</v>
       </c>
       <c r="J26" s="0">
-        <v>1.821862348178136</v>
+        <v>0</v>
       </c>
       <c r="K26" s="0">
-        <v>7.3453608247422615</v>
+        <v>0</v>
       </c>
       <c r="L26" s="0">
-        <v>2.1071128666065357</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="0">
-        <v>3.152997932460369</v>
+        <v>0</v>
       </c>
       <c r="B27" s="0">
-        <v>5.7894736842105212</v>
+        <v>0</v>
       </c>
       <c r="C27" s="0">
-        <v>2.4080954615199257</v>
+        <v>0</v>
       </c>
       <c r="D27" s="0">
-        <v>4.1184814752482355</v>
+        <v>0</v>
       </c>
       <c r="E27" s="0">
-        <v>3.655836987976965</v>
+        <v>0</v>
       </c>
       <c r="F27" s="0">
-        <v>2.7962740603282001</v>
+        <v>0</v>
       </c>
       <c r="G27" s="0">
-        <v>2.6554013277006616</v>
+        <v>0</v>
       </c>
       <c r="H27" s="0">
-        <v>2.9881270238027584</v>
+        <v>0</v>
       </c>
       <c r="I27" s="0">
-        <v>2.4408651268097934</v>
+        <v>0</v>
       </c>
       <c r="J27" s="0">
-        <v>2.7419948472580025</v>
+        <v>0</v>
       </c>
       <c r="K27" s="0">
-        <v>8.8917525773195809</v>
+        <v>0</v>
       </c>
       <c r="L27" s="0">
-        <v>2.8877554194009867</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="0">
-        <v>3.6403465590233304</v>
+        <v>0</v>
       </c>
       <c r="B28" s="0">
-        <v>7.4561403508771855</v>
+        <v>0</v>
       </c>
       <c r="C28" s="0">
-        <v>3.1778237106734775</v>
+        <v>0</v>
       </c>
       <c r="D28" s="0">
-        <v>5.0777775106388052</v>
+        <v>0</v>
       </c>
       <c r="E28" s="0">
-        <v>3.8121662340761922</v>
+        <v>0</v>
       </c>
       <c r="F28" s="0">
-        <v>3.6513481061019504</v>
+        <v>0</v>
       </c>
       <c r="G28" s="0">
-        <v>4.1038020519010221</v>
+        <v>0</v>
       </c>
       <c r="H28" s="0">
-        <v>3.7948077032324004</v>
+        <v>0</v>
       </c>
       <c r="I28" s="0">
-        <v>3.2650791444062652</v>
+        <v>0</v>
       </c>
       <c r="J28" s="0">
-        <v>3.9749723960250241</v>
+        <v>0</v>
       </c>
       <c r="K28" s="0">
-        <v>9.020618556701022</v>
+        <v>0</v>
       </c>
       <c r="L28" s="0">
-        <v>3.5766491462693959</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="0">
-        <v>4.0021659938958543</v>
+        <v>0</v>
       </c>
       <c r="B29" s="0">
-        <v>5.5263157894737098</v>
+        <v>0</v>
       </c>
       <c r="C29" s="0">
-        <v>4.0921137726829091</v>
+        <v>0</v>
       </c>
       <c r="D29" s="0">
-        <v>5.5946914144207218</v>
+        <v>0</v>
       </c>
       <c r="E29" s="0">
-        <v>3.9476118022614224</v>
+        <v>0</v>
       </c>
       <c r="F29" s="0">
-        <v>4.0079321762544309</v>
+        <v>0</v>
       </c>
       <c r="G29" s="0">
-        <v>5.2504526252263366</v>
+        <v>0</v>
       </c>
       <c r="H29" s="0">
-        <v>4.2265522922229364</v>
+        <v>0</v>
       </c>
       <c r="I29" s="0">
-        <v>3.8489801592818598</v>
+        <v>0</v>
       </c>
       <c r="J29" s="0">
-        <v>5.2815605447184639</v>
+        <v>0</v>
       </c>
       <c r="K29" s="0">
-        <v>10.5670103092784</v>
+        <v>0</v>
       </c>
       <c r="L29" s="0">
-        <v>4.049388859515461</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="0">
-        <v>3.9061730826031273</v>
+        <v>0</v>
       </c>
       <c r="B30" s="0">
-        <v>6.3157894736842053</v>
+        <v>0</v>
       </c>
       <c r="C30" s="0">
-        <v>4.4294246693465515</v>
+        <v>0</v>
       </c>
       <c r="D30" s="0">
-        <v>5.9505205202798495</v>
+        <v>0</v>
       </c>
       <c r="E30" s="0">
-        <v>3.7936692622094896</v>
+        <v>0</v>
       </c>
       <c r="F30" s="0">
-        <v>4.1480187752428739</v>
+        <v>0</v>
       </c>
       <c r="G30" s="0">
-        <v>4.6268356467511529</v>
+        <v>0</v>
       </c>
       <c r="H30" s="0">
-        <v>4.5049139351246907</v>
+        <v>0</v>
       </c>
       <c r="I30" s="0">
-        <v>4.6652499453834038</v>
+        <v>0</v>
       </c>
       <c r="J30" s="0">
-        <v>5.1527419948472541</v>
+        <v>0</v>
       </c>
       <c r="K30" s="0">
-        <v>10.438144329896899</v>
+        <v>0</v>
       </c>
       <c r="L30" s="0">
-        <v>4.2904239106770721</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="0">
-        <v>3.7289554002165959</v>
+        <v>0</v>
       </c>
       <c r="B31" s="0">
-        <v>6.4912280701754321</v>
+        <v>0</v>
       </c>
       <c r="C31" s="0">
-        <v>4.5739864822024083</v>
+        <v>0</v>
       </c>
       <c r="D31" s="0">
-        <v>5.4336066164979639</v>
+        <v>0</v>
       </c>
       <c r="E31" s="0">
-        <v>3.637936692622092</v>
+        <v>0</v>
       </c>
       <c r="F31" s="0">
-        <v>4.3645162464068656</v>
+        <v>0</v>
       </c>
       <c r="G31" s="0">
-        <v>4.6268356467511529</v>
+        <v>0</v>
       </c>
       <c r="H31" s="0">
-        <v>4.1583820939612535</v>
+        <v>0</v>
       </c>
       <c r="I31" s="0">
-        <v>4.843995154018784</v>
+        <v>0</v>
       </c>
       <c r="J31" s="0">
-        <v>4.8398969451600982</v>
+        <v>0</v>
       </c>
       <c r="K31" s="0">
-        <v>9.7938144329896826</v>
+        <v>0</v>
       </c>
       <c r="L31" s="0">
-        <v>4.2515472895219695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="0">
-        <v>3.5517377178300653</v>
+        <v>0</v>
       </c>
       <c r="B32" s="0">
-        <v>5.9649122807017489</v>
+        <v>0</v>
       </c>
       <c r="C32" s="0">
-        <v>4.5638417935809441</v>
+        <v>0</v>
       </c>
       <c r="D32" s="0">
-        <v>4.7892674248070541</v>
+        <v>0</v>
       </c>
       <c r="E32" s="0">
-        <v>3.6528536054178193</v>
+        <v>0</v>
       </c>
       <c r="F32" s="0">
-        <v>4.0061128697740385</v>
+        <v>0</v>
       </c>
       <c r="G32" s="0">
-        <v>4.6871856769261679</v>
+        <v>0</v>
       </c>
       <c r="H32" s="0">
-        <v>3.8913821507697519</v>
+        <v>0</v>
       </c>
       <c r="I32" s="0">
-        <v>4.7903715914281699</v>
+        <v>0</v>
       </c>
       <c r="J32" s="0">
-        <v>4.6926757453073202</v>
+        <v>0</v>
       </c>
       <c r="K32" s="0">
-        <v>8.1185567010309203</v>
+        <v>0</v>
       </c>
       <c r="L32" s="0">
-        <v>4.0151774328989482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="0">
-        <v>3.4434380230382953</v>
+        <v>0</v>
       </c>
       <c r="B33" s="0">
-        <v>3.3333333333333304</v>
+        <v>0</v>
       </c>
       <c r="C33" s="0">
-        <v>4.3254416109765499</v>
+        <v>0</v>
       </c>
       <c r="D33" s="0">
-        <v>4.128098478109294</v>
+        <v>0</v>
       </c>
       <c r="E33" s="0">
-        <v>3.4953310062949337</v>
+        <v>0</v>
       </c>
       <c r="F33" s="0">
-        <v>3.8878579485500095</v>
+        <v>0</v>
       </c>
       <c r="G33" s="0">
-        <v>3.6813518406759171</v>
+        <v>0</v>
       </c>
       <c r="H33" s="0">
-        <v>3.6187013577231122</v>
+        <v>0</v>
       </c>
       <c r="I33" s="0">
-        <v>4.6811384083732159</v>
+        <v>0</v>
       </c>
       <c r="J33" s="0">
-        <v>3.8277511961722452</v>
+        <v>0</v>
       </c>
       <c r="K33" s="0">
-        <v>5.4123711340206135</v>
+        <v>0</v>
       </c>
       <c r="L33" s="0">
-        <v>3.7803626411221316</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="0">
-        <v>3.4631288766367989</v>
+        <v>0</v>
       </c>
       <c r="B34" s="0">
-        <v>2.2807017543859631</v>
+        <v>0</v>
       </c>
       <c r="C34" s="0">
-        <v>4.1745393677322777</v>
+        <v>0</v>
       </c>
       <c r="D34" s="0">
-        <v>3.4308657706825638</v>
+        <v>0</v>
       </c>
       <c r="E34" s="0">
-        <v>3.2918643157612073</v>
+        <v>0</v>
       </c>
       <c r="F34" s="0">
-        <v>3.5603827820834666</v>
+        <v>0</v>
       </c>
       <c r="G34" s="0">
-        <v>3.339368336350832</v>
+        <v>0</v>
       </c>
       <c r="H34" s="0">
-        <v>2.8404249275691615</v>
+        <v>0</v>
       </c>
       <c r="I34" s="0">
-        <v>4.4964350261166572</v>
+        <v>0</v>
       </c>
       <c r="J34" s="0">
-        <v>3.2572690467427279</v>
+        <v>0</v>
       </c>
       <c r="K34" s="0">
-        <v>3.0927835051546366</v>
+        <v>0</v>
       </c>
       <c r="L34" s="0">
-        <v>3.7197151121201721</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="0">
-        <v>3.2120704932558977</v>
+        <v>0</v>
       </c>
       <c r="B35" s="0">
-        <v>1.7543859649122888</v>
+        <v>0</v>
       </c>
       <c r="C35" s="0">
-        <v>3.9475519598270514</v>
+        <v>0</v>
       </c>
       <c r="D35" s="0">
-        <v>3.0870579183997449</v>
+        <v>0</v>
       </c>
       <c r="E35" s="0">
-        <v>3.2751573734300101</v>
+        <v>0.001790029535487344</v>
       </c>
       <c r="F35" s="0">
-        <v>3.5239966524760926</v>
+        <v>0</v>
       </c>
       <c r="G35" s="0">
-        <v>2.6755180044256814</v>
+        <v>0</v>
       </c>
       <c r="H35" s="0">
-        <v>2.5450207351019829</v>
+        <v>0</v>
       </c>
       <c r="I35" s="0">
-        <v>4.1925681714365348</v>
+        <v>0</v>
       </c>
       <c r="J35" s="0">
-        <v>2.9260213470739922</v>
+        <v>0</v>
       </c>
       <c r="K35" s="0">
-        <v>2.7061855670103219</v>
+        <v>0</v>
       </c>
       <c r="L35" s="0">
-        <v>3.6855036855037024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="0">
-        <v>3.1948409963571893</v>
+        <v>0</v>
       </c>
       <c r="B36" s="0">
-        <v>1.3157894736842093</v>
+        <v>0</v>
       </c>
       <c r="C36" s="0">
-        <v>3.6787177113582437</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D36" s="0">
-        <v>2.8442285961580049</v>
+        <v>0</v>
       </c>
       <c r="E36" s="0">
-        <v>3.1104746561651573</v>
+        <v>0.003580059070974668</v>
       </c>
       <c r="F36" s="0">
-        <v>3.3802714405268683</v>
+        <v>0</v>
       </c>
       <c r="G36" s="0">
-        <v>2.6352846509756565</v>
+        <v>0</v>
       </c>
       <c r="H36" s="0">
-        <v>2.6359143327841821</v>
+        <v>0</v>
       </c>
       <c r="I36" s="0">
-        <v>4.0694325832654723</v>
+        <v>0.0019860578737264387</v>
       </c>
       <c r="J36" s="0">
-        <v>2.5027603974972377</v>
+        <v>0</v>
       </c>
       <c r="K36" s="0">
-        <v>1.2886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L36" s="0">
-        <v>3.5595434329611511</v>
+        <v>0.0015550648462040854</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="0">
-        <v>3.1456138623609307</v>
+        <v>0</v>
       </c>
       <c r="B37" s="0">
-        <v>0.78947368421052566</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C37" s="0">
-        <v>3.5886835998427542</v>
+        <v>0.001268086077682952</v>
       </c>
       <c r="D37" s="0">
-        <v>3.0654196619623466</v>
+        <v>0.019234005722116688</v>
       </c>
       <c r="E37" s="0">
-        <v>2.9272949670336201</v>
+        <v>0.012530206748411338</v>
       </c>
       <c r="F37" s="0">
-        <v>3.0327839027762589</v>
+        <v>0.0054579194411090446</v>
       </c>
       <c r="G37" s="0">
-        <v>2.5950512975256466</v>
+        <v>0.020116676725005011</v>
       </c>
       <c r="H37" s="0">
-        <v>2.613190933363629</v>
+        <v>0.005680849855138323</v>
       </c>
       <c r="I37" s="0">
-        <v>3.6563325455303737</v>
+        <v>0</v>
       </c>
       <c r="J37" s="0">
-        <v>2.3923444976076533</v>
+        <v>0</v>
       </c>
       <c r="K37" s="0">
-        <v>0.5154639175257727</v>
+        <v>0</v>
       </c>
       <c r="L37" s="0">
-        <v>3.2749665661058036</v>
+        <v>0.0015550648462040854</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="0">
-        <v>3.007777887171406</v>
+        <v>0.0098454267992517386</v>
       </c>
       <c r="B38" s="0">
-        <v>0.87719298245613953</v>
+        <v>0</v>
       </c>
       <c r="C38" s="0">
-        <v>3.195576915761039</v>
+        <v>0.0076085164660977117</v>
       </c>
       <c r="D38" s="0">
-        <v>3.2553554684682489</v>
+        <v>0.038468011444233376</v>
       </c>
       <c r="E38" s="0">
-        <v>2.8007995465258486</v>
+        <v>0.027447119544139122</v>
       </c>
       <c r="F38" s="0">
-        <v>2.9017938361896416</v>
+        <v>0.0072772259214787249</v>
       </c>
       <c r="G38" s="0">
-        <v>2.9772681553007416</v>
+        <v>0</v>
       </c>
       <c r="H38" s="0">
-        <v>2.8404249275691615</v>
+        <v>0</v>
       </c>
       <c r="I38" s="0">
-        <v>3.3683541538400394</v>
+        <v>0.011916347242358632</v>
       </c>
       <c r="J38" s="0">
-        <v>2.2819285977180694</v>
+        <v>0</v>
       </c>
       <c r="K38" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L38" s="0">
-        <v>3.2298696855658848</v>
+        <v>0.012440518769632683</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="0">
-        <v>2.7345672934921703</v>
+        <v>0.03692035049719402</v>
       </c>
       <c r="B39" s="0">
-        <v>0.96491228070175361</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C39" s="0">
-        <v>3.1169555789446961</v>
+        <v>0.016485119009878375</v>
       </c>
       <c r="D39" s="0">
-        <v>3.4813550357031198</v>
+        <v>0.079340273603731332</v>
       </c>
       <c r="E39" s="0">
-        <v>2.7906560458247536</v>
+        <v>0.077567946537784469</v>
       </c>
       <c r="F39" s="0">
-        <v>2.9436378852381448</v>
+        <v>0.034566823127023943</v>
       </c>
       <c r="G39" s="0">
-        <v>3.3192516596258268</v>
+        <v>0.040233353450010022</v>
       </c>
       <c r="H39" s="0">
-        <v>2.8631483269897151</v>
+        <v>0.051127648696244914</v>
       </c>
       <c r="I39" s="0">
-        <v>3.3385632857341432</v>
+        <v>0.023832694484717264</v>
       </c>
       <c r="J39" s="0">
-        <v>2.649981597350016</v>
+        <v>0</v>
       </c>
       <c r="K39" s="0">
         <v>0</v>
       </c>
       <c r="L39" s="0">
-        <v>3.0168258016359255</v>
+        <v>0.021770907846857195</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="0">
-        <v>2.7665649305897388</v>
+        <v>0.046765777296445758</v>
       </c>
       <c r="B40" s="0">
-        <v>0.87719298245613953</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C40" s="0">
-        <v>2.9888788850987176</v>
+        <v>0.062136217806464646</v>
       </c>
       <c r="D40" s="0">
-        <v>3.4500997764046808</v>
+        <v>0.24763782367225232</v>
       </c>
       <c r="E40" s="0">
-        <v>2.6641606253169821</v>
+        <v>0.19093648378531564</v>
       </c>
       <c r="F40" s="0">
-        <v>2.8181057380926364</v>
+        <v>0.076410872175526626</v>
       </c>
       <c r="G40" s="0">
-        <v>2.9370348018507317</v>
+        <v>0.080466706900020044</v>
       </c>
       <c r="H40" s="0">
-        <v>3.1301482701812162</v>
+        <v>0.090893597682213168</v>
       </c>
       <c r="I40" s="0">
-        <v>2.9532680582312145</v>
+        <v>0.08341443069651043</v>
       </c>
       <c r="J40" s="0">
-        <v>3.091645196908352</v>
+        <v>0</v>
       </c>
       <c r="K40" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L40" s="0">
-        <v>2.7400242590115984</v>
+        <v>0.076198177464000191</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="0">
-        <v>2.6533425223983582</v>
+        <v>0.13783597518952512</v>
       </c>
       <c r="B41" s="0">
-        <v>0.26315789473684331</v>
+        <v>1.0526315789473733</v>
       </c>
       <c r="C41" s="0">
-        <v>2.8341723836214134</v>
+        <v>0.19021291165244386</v>
       </c>
       <c r="D41" s="0">
-        <v>3.3827807563772909</v>
+        <v>0.50248839949030111</v>
       </c>
       <c r="E41" s="0">
-        <v>2.5686923834243385</v>
+        <v>0.38127629105880423</v>
       </c>
       <c r="F41" s="0">
-        <v>2.6288978641342045</v>
+        <v>0.18556926099770854</v>
       </c>
       <c r="G41" s="0">
-        <v>2.796218064775712</v>
+        <v>0.2011667672500512</v>
       </c>
       <c r="H41" s="0">
-        <v>3.0960631710504036</v>
+        <v>0.21587229449525752</v>
       </c>
       <c r="I41" s="0">
-        <v>2.9572401739786836</v>
+        <v>0.13505193541339858</v>
       </c>
       <c r="J41" s="0">
-        <v>3.0180345969819795</v>
+        <v>0.11041589988958463</v>
       </c>
       <c r="K41" s="0">
-        <v>0</v>
+        <v>0.77319587628866338</v>
       </c>
       <c r="L41" s="0">
-        <v>2.6700463409324295</v>
+        <v>0.16483687369763395</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="0">
-        <v>2.7665649305897388</v>
+        <v>0.32982179777493326</v>
       </c>
       <c r="B42" s="0">
-        <v>0.35087719298245584</v>
+        <v>2.1929824561403488</v>
       </c>
       <c r="C42" s="0">
-        <v>2.6541041605904185</v>
+        <v>0.39057051192634923</v>
       </c>
       <c r="D42" s="0">
-        <v>2.9139518669006779</v>
+        <v>1.0145938018416552</v>
       </c>
       <c r="E42" s="0">
-        <v>2.4875443778155648</v>
+        <v>0.76792267072406628</v>
       </c>
       <c r="F42" s="0">
-        <v>2.4687988938616576</v>
+        <v>0.3765964414365241</v>
       </c>
       <c r="G42" s="0">
-        <v>2.6151679742506517</v>
+        <v>0.30175015087507517</v>
       </c>
       <c r="H42" s="0">
-        <v>2.7211270806112573</v>
+        <v>0.47719138783161919</v>
       </c>
       <c r="I42" s="0">
-        <v>2.7645925602272023</v>
+        <v>0.37139282238684401</v>
       </c>
       <c r="J42" s="0">
-        <v>2.7972027972027949</v>
+        <v>0.40485829959514136</v>
       </c>
       <c r="K42" s="0">
-        <v>0</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L42" s="0">
-        <v>2.5192050508506179</v>
+        <v>0.37788075762759271</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="0">
-        <v>2.5105838338091933</v>
+        <v>0.65964359554986651</v>
       </c>
       <c r="B43" s="0">
-        <v>1.2280701754385954</v>
+        <v>2.8947368421052606</v>
       </c>
       <c r="C43" s="0">
-        <v>2.510810433812245</v>
+        <v>0.73422183897842919</v>
       </c>
       <c r="D43" s="0">
-        <v>2.4451229774240835</v>
+        <v>1.6757627485394162</v>
       </c>
       <c r="E43" s="0">
-        <v>2.4040096661594892</v>
+        <v>1.2052865538948048</v>
       </c>
       <c r="F43" s="0">
-        <v>2.2923261652657989</v>
+        <v>0.80777207728413858</v>
       </c>
       <c r="G43" s="0">
-        <v>2.5347012673506315</v>
+        <v>0.78455039227519552</v>
       </c>
       <c r="H43" s="0">
-        <v>2.3916377890132341</v>
+        <v>0.99414872464920667</v>
       </c>
       <c r="I43" s="0">
-        <v>2.5123632102639446</v>
+        <v>0.80633949673293415</v>
       </c>
       <c r="J43" s="0">
-        <v>2.6131762973868211</v>
+        <v>0.88332719911667212</v>
       </c>
       <c r="K43" s="0">
-        <v>0</v>
+        <v>2.7061855670103068</v>
       </c>
       <c r="L43" s="0">
-        <v>2.4912138836189448</v>
+        <v>0.68267346748359348</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="0">
-        <v>2.3112139411243455</v>
+        <v>1.1051491582160076</v>
       </c>
       <c r="B44" s="0">
-        <v>1.2280701754385954</v>
+        <v>4.736842105263154</v>
       </c>
       <c r="C44" s="0">
-        <v>2.2977719727615091</v>
+        <v>1.3276861233340509</v>
       </c>
       <c r="D44" s="0">
-        <v>2.0676556151275438</v>
+        <v>2.6542927896521027</v>
       </c>
       <c r="E44" s="0">
-        <v>2.3497121035830402</v>
+        <v>1.7924162415346505</v>
       </c>
       <c r="F44" s="0">
-        <v>2.3141578430302348</v>
+        <v>1.3626605537968914</v>
       </c>
       <c r="G44" s="0">
-        <v>1.9312009656004812</v>
+        <v>1.2271172802253056</v>
       </c>
       <c r="H44" s="0">
-        <v>2.124637845821733</v>
+        <v>1.6247230585695605</v>
       </c>
       <c r="I44" s="0">
-        <v>2.3395761752497446</v>
+        <v>1.2968957915433643</v>
       </c>
       <c r="J44" s="0">
-        <v>2.189915347810083</v>
+        <v>1.0489510489510481</v>
       </c>
       <c r="K44" s="0">
-        <v>0</v>
+        <v>3.3505154639175228</v>
       </c>
       <c r="L44" s="0">
-        <v>2.2735048051503726</v>
+        <v>1.1818492831151048</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="0">
-        <v>2.2841390174264036</v>
+        <v>1.7451019001673707</v>
       </c>
       <c r="B45" s="0">
-        <v>2.7192982456140329</v>
+        <v>7.5438596491228003</v>
       </c>
       <c r="C45" s="0">
-        <v>2.2242229802558979</v>
+        <v>1.8932525139806475</v>
       </c>
       <c r="D45" s="0">
-        <v>1.8392517971774081</v>
+        <v>3.9622051787560371</v>
       </c>
       <c r="E45" s="0">
-        <v>2.2542438616903824</v>
+        <v>2.4988812315403179</v>
       </c>
       <c r="F45" s="0">
-        <v>2.1049375977877216</v>
+        <v>2.0758286941018067</v>
       </c>
       <c r="G45" s="0">
-        <v>1.7501508750754358</v>
+        <v>2.2128344397505515</v>
       </c>
       <c r="H45" s="0">
-        <v>1.9258081008918917</v>
+        <v>2.3405101403169892</v>
       </c>
       <c r="I45" s="0">
-        <v>2.2521896288057812</v>
+        <v>1.9542809477468157</v>
       </c>
       <c r="J45" s="0">
-        <v>2.0058888479941093</v>
+        <v>2.0426941479573042</v>
       </c>
       <c r="K45" s="0">
-        <v>0</v>
+        <v>5.9278350515463867</v>
       </c>
       <c r="L45" s="0">
-        <v>2.1910863683015562</v>
+        <v>1.9018443069075963</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="0">
-        <v>2.2447573102293963</v>
+        <v>2.6705720192970341</v>
       </c>
       <c r="B46" s="0">
-        <v>2.1052631578947349</v>
+        <v>6.7543859649122746</v>
       </c>
       <c r="C46" s="0">
-        <v>2.1417973852065058</v>
+        <v>2.7783765962033478</v>
       </c>
       <c r="D46" s="0">
-        <v>1.7022095064073268</v>
+        <v>5.0008414877503382</v>
       </c>
       <c r="E46" s="0">
-        <v>2.1695157970106487</v>
+        <v>3.1426951878039295</v>
       </c>
       <c r="F46" s="0">
-        <v>1.9812247571225832</v>
+        <v>2.7271404140741526</v>
       </c>
       <c r="G46" s="0">
-        <v>1.589217461275396</v>
+        <v>3.1180848923757769</v>
       </c>
       <c r="H46" s="0">
-        <v>1.9826165994432752</v>
+        <v>3.3119354655456426</v>
       </c>
       <c r="I46" s="0">
-        <v>2.1926078925939883</v>
+        <v>2.8917002641456944</v>
       </c>
       <c r="J46" s="0">
-        <v>1.5826278984173707</v>
+        <v>3.0180345969819626</v>
       </c>
       <c r="K46" s="0">
-        <v>0.25773195876288635</v>
+        <v>8.2474226804123632</v>
       </c>
       <c r="L46" s="0">
-        <v>1.9345006686778823</v>
+        <v>2.679376730009639</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="0">
-        <v>2.0773850546421282</v>
+        <v>3.1997637097568328</v>
       </c>
       <c r="B47" s="0">
-        <v>3.2456140350877343</v>
+        <v>6.3157894736842399</v>
       </c>
       <c r="C47" s="0">
-        <v>2.0695164787785889</v>
+        <v>3.6000963745419203</v>
       </c>
       <c r="D47" s="0">
-        <v>1.642103238525721</v>
+        <v>5.6980741951770995</v>
       </c>
       <c r="E47" s="0">
-        <v>2.0752409081416605</v>
+        <v>3.5902025716757824</v>
       </c>
       <c r="F47" s="0">
-        <v>1.999417821926291</v>
+        <v>3.4457664738201959</v>
       </c>
       <c r="G47" s="0">
-        <v>2.1726010863005532</v>
+        <v>4.425668879501127</v>
       </c>
       <c r="H47" s="0">
-        <v>1.8235528034994122</v>
+        <v>3.9311480997557418</v>
       </c>
       <c r="I47" s="0">
-        <v>2.0476256678119698</v>
+        <v>3.648388314035488</v>
       </c>
       <c r="J47" s="0">
-        <v>1.6010305483989768</v>
+        <v>4.140596245859423</v>
       </c>
       <c r="K47" s="0">
-        <v>0</v>
+        <v>8.5051546391752986</v>
       </c>
       <c r="L47" s="0">
-        <v>2.020029235219118</v>
+        <v>3.3807109756477005</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="0">
-        <v>2.1512257556365051</v>
+        <v>3.5886580683272587</v>
       </c>
       <c r="B48" s="0">
-        <v>4.122807017543856</v>
+        <v>5.7017543859649065</v>
       </c>
       <c r="C48" s="0">
-        <v>1.9794823672630881</v>
+        <v>4.2569649627816704</v>
       </c>
       <c r="D48" s="0">
-        <v>1.723847762844708</v>
+        <v>5.9336907652729973</v>
       </c>
       <c r="E48" s="0">
-        <v>2.0961245860556681</v>
+        <v>3.871237208747274</v>
       </c>
       <c r="F48" s="0">
-        <v>1.8757049812611415</v>
+        <v>3.9242440781574031</v>
       </c>
       <c r="G48" s="0">
-        <v>2.0116676725005012</v>
+        <v>5.069402534701263</v>
       </c>
       <c r="H48" s="0">
-        <v>1.9030847014713383</v>
+        <v>4.3799352383116474</v>
       </c>
       <c r="I48" s="0">
-        <v>1.9165458481460131</v>
+        <v>4.4011042481777878</v>
       </c>
       <c r="J48" s="0">
-        <v>1.4722119985277868</v>
+        <v>5.6680161943319787</v>
       </c>
       <c r="K48" s="0">
-        <v>0.38659793814432958</v>
+        <v>11.597938144329888</v>
       </c>
       <c r="L48" s="0">
-        <v>1.7898796379809021</v>
+        <v>3.9591950984356013</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="0">
-        <v>1.9075514423550246</v>
+        <v>4.0686226247907813</v>
       </c>
       <c r="B49" s="0">
-        <v>3.5964912280701724</v>
+        <v>6.4912280701754321</v>
       </c>
       <c r="C49" s="0">
-        <v>1.8957886861360134</v>
+        <v>4.4623949073663081</v>
       </c>
       <c r="D49" s="0">
-        <v>1.8945495636284935</v>
+        <v>5.6019041665664844</v>
       </c>
       <c r="E49" s="0">
-        <v>1.8705808645842641</v>
+        <v>3.8939109161967807</v>
       </c>
       <c r="F49" s="0">
-        <v>1.8320416257322691</v>
+        <v>4.3317687297602117</v>
       </c>
       <c r="G49" s="0">
-        <v>1.9312009656004812</v>
+        <v>4.6268356467511529</v>
       </c>
       <c r="H49" s="0">
-        <v>1.9882974492984133</v>
+        <v>4.5446798841106588</v>
       </c>
       <c r="I49" s="0">
-        <v>1.864908343429126</v>
+        <v>4.8003018807968019</v>
       </c>
       <c r="J49" s="0">
-        <v>1.5826278984173707</v>
+        <v>4.950312845049683</v>
       </c>
       <c r="K49" s="0">
-        <v>0.12886597938144317</v>
+        <v>10.309278350515454</v>
       </c>
       <c r="L49" s="0">
-        <v>1.6996858769010652</v>
+        <v>4.2048953441358465</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="0">
-        <v>1.956778576351283</v>
+        <v>3.7806438909126676</v>
       </c>
       <c r="B50" s="0">
-        <v>1.9298245614035072</v>
+        <v>4.5614035087719263</v>
       </c>
       <c r="C50" s="0">
-        <v>1.7626396479793032</v>
+        <v>4.5739864822024083</v>
       </c>
       <c r="D50" s="0">
-        <v>1.7286562642752372</v>
+        <v>5.0032457384656031</v>
       </c>
       <c r="E50" s="0">
-        <v>1.8574539813240234</v>
+        <v>3.854530266416059</v>
       </c>
       <c r="F50" s="0">
-        <v>1.7519921405960033</v>
+        <v>4.2990212131135568</v>
       </c>
       <c r="G50" s="0">
-        <v>2.3134178233755764</v>
+        <v>4.7676523838261877</v>
       </c>
       <c r="H50" s="0">
-        <v>1.9769357495881366</v>
+        <v>4.2322331420780506</v>
       </c>
       <c r="I50" s="0">
-        <v>1.6106929355921416</v>
+        <v>4.9154932374729352</v>
       </c>
       <c r="J50" s="0">
-        <v>1.7482517482517468</v>
+        <v>5.1895472948104482</v>
       </c>
       <c r="K50" s="0">
-        <v>0.38659793814432958</v>
+        <v>9.6649484536082397</v>
       </c>
       <c r="L50" s="0">
-        <v>1.7354523683637593</v>
+        <v>4.3712872826796838</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="0">
-        <v>1.816481244461946</v>
+        <v>3.6452692724229561</v>
       </c>
       <c r="B51" s="0">
-        <v>1.8421052631578929</v>
+        <v>2.7192982456140329</v>
       </c>
       <c r="C51" s="0">
-        <v>1.6573885035316183</v>
+        <v>4.6665567658732634</v>
       </c>
       <c r="D51" s="0">
-        <v>1.5892097227898911</v>
+        <v>4.1184814752482355</v>
       </c>
       <c r="E51" s="0">
-        <v>1.7351352963990556</v>
+        <v>3.6814940779856165</v>
       </c>
       <c r="F51" s="0">
-        <v>1.7247025433904579</v>
+        <v>4.2862860677509698</v>
       </c>
       <c r="G51" s="0">
-        <v>1.4282840474753558</v>
+        <v>4.2043854355260475</v>
       </c>
       <c r="H51" s="0">
-        <v>1.8974038516162002</v>
+        <v>3.93114809975572</v>
       </c>
       <c r="I51" s="0">
-        <v>1.4657107108101117</v>
+        <v>4.7625667811959991</v>
       </c>
       <c r="J51" s="0">
-        <v>1.601030548398968</v>
+        <v>4.5086492454913465</v>
       </c>
       <c r="K51" s="0">
-        <v>0.38659793814432958</v>
+        <v>8.5051546391752506</v>
       </c>
       <c r="L51" s="0">
-        <v>1.6110471806674325</v>
+        <v>4.2577675489067852</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0">
-        <v>1.6540317022742921</v>
+        <v>3.583735354927633</v>
       </c>
       <c r="B52" s="0">
-        <v>1.4912280701754372</v>
+        <v>2.0175438596491211</v>
       </c>
       <c r="C52" s="0">
-        <v>1.630758695900276</v>
+        <v>4.2709139096361826</v>
       </c>
       <c r="D52" s="0">
-        <v>1.4377419277282222</v>
+        <v>3.5078017935710308</v>
       </c>
       <c r="E52" s="0">
-        <v>1.6533906142784673</v>
+        <v>3.6677705182135472</v>
       </c>
       <c r="F52" s="0">
-        <v>1.588254557362732</v>
+        <v>3.8987737874322277</v>
       </c>
       <c r="G52" s="0">
-        <v>1.4484007242003607</v>
+        <v>3.3192516596258268</v>
       </c>
       <c r="H52" s="0">
-        <v>1.8917230017610618</v>
+        <v>3.4255524626484095</v>
       </c>
       <c r="I52" s="0">
-        <v>1.3922265694822336</v>
+        <v>4.5182816627276479</v>
       </c>
       <c r="J52" s="0">
-        <v>1.9322782480677201</v>
+        <v>3.7909458962090508</v>
       </c>
       <c r="K52" s="0">
-        <v>1.1597938144329887</v>
+        <v>5.6701030927835001</v>
       </c>
       <c r="L52" s="0">
-        <v>1.5472895219730649</v>
+        <v>3.9327589960501319</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0">
-        <v>1.58511371467953</v>
+        <v>3.3499064684454041</v>
       </c>
       <c r="B53" s="0">
-        <v>1.3157894736842093</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C53" s="0">
-        <v>1.5229713792972253</v>
+        <v>4.0325137270317875</v>
       </c>
       <c r="D53" s="0">
-        <v>1.0939340754453866</v>
+        <v>3.0702281633928759</v>
       </c>
       <c r="E53" s="0">
-        <v>1.5615024314567845</v>
+        <v>3.5305349204928516</v>
       </c>
       <c r="F53" s="0">
-        <v>1.5209402175890536</v>
+        <v>3.6840956227486048</v>
       </c>
       <c r="G53" s="0">
-        <v>1.5087507543753758</v>
+        <v>3.5405351036008819</v>
       </c>
       <c r="H53" s="0">
-        <v>1.6360847582798372</v>
+        <v>2.7097653809009805</v>
       </c>
       <c r="I53" s="0">
-        <v>1.4021568588508657</v>
+        <v>4.3296061647236366</v>
       </c>
       <c r="J53" s="0">
-        <v>1.6562384983437601</v>
+        <v>3.091645196908352</v>
       </c>
       <c r="K53" s="0">
-        <v>0.90206185567010222</v>
+        <v>3.6082474226804089</v>
       </c>
       <c r="L53" s="0">
-        <v>1.3342456380431051</v>
+        <v>3.6917239448884982</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0">
-        <v>1.4325095992911281</v>
+        <v>3.5541990745298779</v>
       </c>
       <c r="B54" s="0">
         <v>1.0526315789473675</v>
       </c>
       <c r="C54" s="0">
-        <v>1.3784095664413689</v>
+        <v>3.775092253262148</v>
       </c>
       <c r="D54" s="0">
-        <v>0.91842377323107172</v>
+        <v>2.8610583511648566</v>
       </c>
       <c r="E54" s="0">
-        <v>1.5185417226050884</v>
+        <v>3.4016527939377634</v>
       </c>
       <c r="F54" s="0">
-        <v>1.3972273769239154</v>
+        <v>3.6040461376123387</v>
       </c>
       <c r="G54" s="0">
-        <v>1.1265338966002805</v>
+        <v>2.4743512371756164</v>
       </c>
       <c r="H54" s="0">
-        <v>1.3861273646537509</v>
+        <v>2.3348292904618511</v>
       </c>
       <c r="I54" s="0">
-        <v>1.1916347242358631</v>
+        <v>4.1012095092450958</v>
       </c>
       <c r="J54" s="0">
-        <v>1.8586676481413307</v>
+        <v>2.7603974972395999</v>
       </c>
       <c r="K54" s="0">
-        <v>0.64432989690721587</v>
+        <v>2.8350515463917501</v>
       </c>
       <c r="L54" s="0">
-        <v>1.4026684912760849</v>
+        <v>3.6823935558112742</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0">
-        <v>1.4472777394900056</v>
+        <v>3.2711430540513904</v>
       </c>
       <c r="B55" s="0">
-        <v>0.52631578947368374</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C55" s="0">
-        <v>1.2909116270812451</v>
+        <v>3.6000963745419003</v>
       </c>
       <c r="D55" s="0">
-        <v>0.8390834996273403</v>
+        <v>3.0269516505181135</v>
       </c>
       <c r="E55" s="0">
-        <v>1.3634058295295193</v>
+        <v>3.2775440794773081</v>
       </c>
       <c r="F55" s="0">
-        <v>1.273514536258777</v>
+        <v>3.302041261870972</v>
       </c>
       <c r="G55" s="0">
-        <v>1.4484007242003607</v>
+        <v>2.3335345001005816</v>
       </c>
       <c r="H55" s="0">
-        <v>1.3918082145088893</v>
+        <v>2.2893824916207444</v>
       </c>
       <c r="I55" s="0">
-        <v>1.1459553931401552</v>
+        <v>3.6821512978888173</v>
       </c>
       <c r="J55" s="0">
-        <v>1.3065881486934106</v>
+        <v>2.3003312476996665</v>
       </c>
       <c r="K55" s="0">
-        <v>0.5154639175257727</v>
+        <v>1.417525773195875</v>
       </c>
       <c r="L55" s="0">
-        <v>1.2627126551177172</v>
+        <v>3.5082262930364165</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0">
-        <v>1.3955892487939339</v>
+        <v>3.1923796396573763</v>
       </c>
       <c r="B56" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C56" s="0">
-        <v>1.2300434953524635</v>
+        <v>3.3959345160349454</v>
       </c>
       <c r="D56" s="0">
-        <v>0.77416873031519662</v>
+        <v>3.2000577020171637</v>
       </c>
       <c r="E56" s="0">
-        <v>1.2929980011336843</v>
+        <v>3.0591604761478539</v>
       </c>
       <c r="F56" s="0">
-        <v>1.2844303751409951</v>
+        <v>3.0491576610995863</v>
       </c>
       <c r="G56" s="0">
-        <v>1.3679340173003409</v>
+        <v>3.0979682156507717</v>
       </c>
       <c r="H56" s="0">
-        <v>1.2952337669715377</v>
+        <v>2.4995739362608624</v>
       </c>
       <c r="I56" s="0">
-        <v>1.0744573096860033</v>
+        <v>3.5510714782228723</v>
       </c>
       <c r="J56" s="0">
-        <v>1.0673536989326453</v>
+        <v>2.0058888479941093</v>
       </c>
       <c r="K56" s="0">
-        <v>0.38659793814432958</v>
+        <v>0.5154639175257727</v>
       </c>
       <c r="L56" s="0">
-        <v>1.2704879793487378</v>
+        <v>3.2656361770285796</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0">
-        <v>1.2454464901053588</v>
+        <v>3.0471595943684471</v>
       </c>
       <c r="B57" s="0">
-        <v>0.17543859649122986</v>
+        <v>1.315789473684224</v>
       </c>
       <c r="C57" s="0">
-        <v>1.159030675002231</v>
+        <v>3.1714832802850985</v>
       </c>
       <c r="D57" s="0">
-        <v>0.73329646815570682</v>
+        <v>3.4068232635299553</v>
       </c>
       <c r="E57" s="0">
-        <v>1.1736626987678749</v>
+        <v>3.0191831498553365</v>
       </c>
       <c r="F57" s="0">
-        <v>1.2680566168176819</v>
+        <v>2.7962740603282312</v>
       </c>
       <c r="G57" s="0">
-        <v>1.2271172802253194</v>
+        <v>3.1180848923758116</v>
       </c>
       <c r="H57" s="0">
-        <v>1.3463614156677977</v>
+        <v>2.8404249275691931</v>
       </c>
       <c r="I57" s="0">
-        <v>1.0406943258326653</v>
+        <v>3.3981450219459744</v>
       </c>
       <c r="J57" s="0">
-        <v>1.1777695988222423</v>
+        <v>2.5211630474788627</v>
       </c>
       <c r="K57" s="0">
-        <v>0.25773195876288924</v>
+        <v>0</v>
       </c>
       <c r="L57" s="0">
-        <v>1.1507479861910359</v>
+        <v>3.2220943613349009</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0">
-        <v>1.13222408191395</v>
+        <v>2.9339371861770181</v>
       </c>
       <c r="B58" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C58" s="0">
-        <v>1.0791412521081922</v>
+        <v>3.063695963682012</v>
       </c>
       <c r="D58" s="0">
-        <v>0.68521145385040694</v>
+        <v>3.5294400500084122</v>
       </c>
       <c r="E58" s="0">
-        <v>1.0734210447805712</v>
+        <v>2.8920910528357022</v>
       </c>
       <c r="F58" s="0">
-        <v>1.1498016955936388</v>
+        <v>2.9218062074737086</v>
       </c>
       <c r="G58" s="0">
-        <v>1.1868839267752955</v>
+        <v>3.178434922550792</v>
       </c>
       <c r="H58" s="0">
-        <v>1.1702550701584946</v>
+        <v>3.0960631710503863</v>
       </c>
       <c r="I58" s="0">
-        <v>0.92550296915652042</v>
+        <v>3.1121526881293291</v>
       </c>
       <c r="J58" s="0">
-        <v>1.10415899889584</v>
+        <v>2.7235921972764054</v>
       </c>
       <c r="K58" s="0">
         <v>0</v>
       </c>
       <c r="L58" s="0">
-        <v>1.0838801978042474</v>
+        <v>2.9173016514788639</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0">
-        <v>1.0460765974204973</v>
+        <v>2.9142463325785148</v>
       </c>
       <c r="B59" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C59" s="0">
-        <v>1.0410986697777036</v>
+        <v>2.9343511837583511</v>
       </c>
       <c r="D59" s="0">
-        <v>0.71165821171831734</v>
+        <v>3.1856321977255764</v>
       </c>
       <c r="E59" s="0">
-        <v>1.0071899519675398</v>
+        <v>2.7733524269817096</v>
       </c>
       <c r="F59" s="0">
-        <v>1.1789105992795537</v>
+        <v>2.8726849325037267</v>
       </c>
       <c r="G59" s="0">
-        <v>1.3075839871253259</v>
+        <v>3.1382015691007821</v>
       </c>
       <c r="H59" s="0">
-        <v>1.2554678179855696</v>
+        <v>3.1187865704709399</v>
       </c>
       <c r="I59" s="0">
-        <v>0.859963059323548</v>
+        <v>2.8738257432821564</v>
       </c>
       <c r="J59" s="0">
-        <v>1.159366948840632</v>
+        <v>2.7972027972027949</v>
       </c>
       <c r="K59" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L59" s="0">
-        <v>1.0325630578795126</v>
+        <v>2.7789008801667006</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0">
-        <v>0.99438810672442568</v>
+        <v>2.7690262872895515</v>
       </c>
       <c r="B60" s="0">
-        <v>0.61403508771929771</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C60" s="0">
-        <v>0.97642627981587315</v>
+        <v>2.7821808544363966</v>
       </c>
       <c r="D60" s="0">
-        <v>0.66597744812829018</v>
+        <v>3.0341644026639072</v>
       </c>
       <c r="E60" s="0">
-        <v>0.9421522121781668</v>
+        <v>2.626570005071748</v>
       </c>
       <c r="F60" s="0">
-        <v>1.131608630789942</v>
+        <v>2.5615835243605112</v>
       </c>
       <c r="G60" s="0">
-        <v>1.1667672500502908</v>
+        <v>2.9772681553007416</v>
       </c>
       <c r="H60" s="0">
-        <v>1.2497869681304312</v>
+        <v>2.8120206782934703</v>
       </c>
       <c r="I60" s="0">
-        <v>0.81428372822783979</v>
+        <v>2.8301324700601751</v>
       </c>
       <c r="J60" s="0">
-        <v>1.10415899889584</v>
+        <v>2.9628266470371707</v>
       </c>
       <c r="K60" s="0">
         <v>0</v>
       </c>
       <c r="L60" s="0">
-        <v>0.99057630703200239</v>
+        <v>2.6762666003172306</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0">
-        <v>0.96239046962685748</v>
+        <v>2.7148764398936671</v>
       </c>
       <c r="B61" s="0">
-        <v>0.26315789473684187</v>
+        <v>1.3157894736842093</v>
       </c>
       <c r="C61" s="0">
-        <v>0.94472412787379911</v>
+        <v>2.5513891882980992</v>
       </c>
       <c r="D61" s="0">
-        <v>0.50008414877503382</v>
+        <v>2.6062077753468107</v>
       </c>
       <c r="E61" s="0">
-        <v>0.83952385214355962</v>
+        <v>2.5901727378501724</v>
       </c>
       <c r="F61" s="0">
-        <v>1.0151730160462822</v>
+        <v>2.3960266346468706</v>
       </c>
       <c r="G61" s="0">
-        <v>0.84490042245021046</v>
+        <v>2.2731844699255661</v>
       </c>
       <c r="H61" s="0">
-        <v>1.2611486678407078</v>
+        <v>2.7324887803215336</v>
       </c>
       <c r="I61" s="0">
-        <v>0.75867410776349953</v>
+        <v>2.6275545669400784</v>
       </c>
       <c r="J61" s="0">
-        <v>0.90172984909826925</v>
+        <v>2.8708133971291843</v>
       </c>
       <c r="K61" s="0">
         <v>0</v>
       </c>
       <c r="L61" s="0">
-        <v>0.92837371318383899</v>
+        <v>2.6964824433178838</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="0">
-        <v>0.78763414394013909</v>
+        <v>2.7345672934921703</v>
       </c>
       <c r="B62" s="0">
-        <v>0.61403508771929771</v>
+        <v>2.105263157894735</v>
       </c>
       <c r="C62" s="0">
-        <v>0.86103044674672435</v>
+        <v>2.400486945053828</v>
       </c>
       <c r="D62" s="0">
-        <v>0.47363739090712337</v>
+        <v>2.0844853701343959</v>
       </c>
       <c r="E62" s="0">
-        <v>0.72197857931322473</v>
+        <v>2.4976878785166599</v>
       </c>
       <c r="F62" s="0">
-        <v>0.9569552086744525</v>
+        <v>2.4178583124113065</v>
       </c>
       <c r="G62" s="0">
-        <v>0.92536712935023058</v>
+        <v>2.1726010863005412</v>
       </c>
       <c r="H62" s="0">
-        <v>1.0509572232005899</v>
+        <v>2.2325739930693609</v>
       </c>
       <c r="I62" s="0">
-        <v>0.69313419793052711</v>
+        <v>2.5878334094655497</v>
       </c>
       <c r="J62" s="0">
-        <v>1.0305483989694506</v>
+        <v>2.5027603974972377</v>
       </c>
       <c r="K62" s="0">
         <v>0</v>
       </c>
       <c r="L62" s="0">
-        <v>0.92059838895281854</v>
+        <v>2.478773364849312</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="0">
-        <v>0.78763414394013909</v>
+        <v>2.5524268977060132</v>
       </c>
       <c r="B63" s="0">
-        <v>0.70175438596491169</v>
+        <v>1.7543859649122791</v>
       </c>
       <c r="C63" s="0">
-        <v>0.84327724165916307</v>
+        <v>2.4144358919083406</v>
       </c>
       <c r="D63" s="0">
-        <v>0.46402038804606505</v>
+        <v>1.7935710335873809</v>
       </c>
       <c r="E63" s="0">
-        <v>0.68259792953250342</v>
+        <v>2.3634356633551099</v>
       </c>
       <c r="F63" s="0">
-        <v>0.86780919113633803</v>
+        <v>2.1813484699632482</v>
       </c>
       <c r="G63" s="0">
-        <v>0.56326694830014024</v>
+        <v>1.6093341380004007</v>
       </c>
       <c r="H63" s="0">
-        <v>0.86917002783616348</v>
+        <v>2.1814463443731165</v>
       </c>
       <c r="I63" s="0">
-        <v>0.69710631367797993</v>
+        <v>2.3395761752497446</v>
       </c>
       <c r="J63" s="0">
-        <v>1.0673536989326453</v>
+        <v>2.3187338976812639</v>
       </c>
       <c r="K63" s="0">
         <v>0</v>
       </c>
       <c r="L63" s="0">
-        <v>0.81640904425714489</v>
+        <v>2.3761390849998421</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="0">
-        <v>0.7236388697450028</v>
+        <v>2.5056611204095676</v>
       </c>
       <c r="B64" s="0">
-        <v>0.61403508771929771</v>
+        <v>3.2456140350877161</v>
       </c>
       <c r="C64" s="0">
-        <v>0.73675801113379513</v>
+        <v>2.1658910206824817</v>
       </c>
       <c r="D64" s="0">
-        <v>0.29812708869280863</v>
+        <v>1.6372947370951829</v>
       </c>
       <c r="E64" s="0">
-        <v>0.58295295205704178</v>
+        <v>2.3210716310152431</v>
       </c>
       <c r="F64" s="0">
-        <v>0.79685623840192055</v>
+        <v>2.2104573736491626</v>
       </c>
       <c r="G64" s="0">
-        <v>0.86501709917521541</v>
+        <v>2.051901025950511</v>
       </c>
       <c r="H64" s="0">
-        <v>0.75555303073339708</v>
+        <v>2.0337442481395196</v>
       </c>
       <c r="I64" s="0">
-        <v>0.60971976723401666</v>
+        <v>2.1747333717304502</v>
       </c>
       <c r="J64" s="0">
-        <v>0.68089804931910136</v>
+        <v>1.9322782480677201</v>
       </c>
       <c r="K64" s="0">
         <v>0</v>
       </c>
       <c r="L64" s="0">
-        <v>0.77597735825583858</v>
+        <v>2.2144123409946173</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="0">
-        <v>0.72610022644481576</v>
+        <v>2.2693708772275256</v>
       </c>
       <c r="B65" s="0">
-        <v>1.4035087719298234</v>
+        <v>3.3333333333333304</v>
       </c>
       <c r="C65" s="0">
-        <v>0.69998351488098953</v>
+        <v>2.1341888687404085</v>
       </c>
       <c r="D65" s="0">
-        <v>0.31976534513018989</v>
+        <v>1.7551030221431474</v>
       </c>
       <c r="E65" s="0">
-        <v>0.5769861869387507</v>
+        <v>2.2542438616903824</v>
       </c>
       <c r="F65" s="0">
-        <v>0.69315576902084863</v>
+        <v>2.0321653385729341</v>
       </c>
       <c r="G65" s="0">
-        <v>0.74431703882518541</v>
+        <v>1.569100784550391</v>
       </c>
       <c r="H65" s="0">
-        <v>0.67602113276146047</v>
+        <v>1.6815315571209437</v>
       </c>
       <c r="I65" s="0">
-        <v>0.583901014875573</v>
+        <v>2.0595420150543169</v>
       </c>
       <c r="J65" s="0">
-        <v>0.69930069930069871</v>
+        <v>1.601030548398968</v>
       </c>
       <c r="K65" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L65" s="0">
-        <v>0.71532982925387922</v>
+        <v>2.0620159860666174</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="0">
-        <v>0.59318696465491727</v>
+        <v>2.22260509993108</v>
       </c>
       <c r="B66" s="0">
-        <v>1.4035087719298234</v>
+        <v>3.3333333333333304</v>
       </c>
       <c r="C66" s="0">
-        <v>0.69744734272562359</v>
+        <v>2.1088271471867492</v>
       </c>
       <c r="D66" s="0">
-        <v>0.24282932224172316</v>
+        <v>1.8055922871637036</v>
       </c>
       <c r="E66" s="0">
-        <v>0.49583818132999147</v>
+        <v>2.1903994749246678</v>
       </c>
       <c r="F66" s="0">
-        <v>0.70589091438343643</v>
+        <v>1.897536659025578</v>
       </c>
       <c r="G66" s="0">
-        <v>0.82478374572520541</v>
+        <v>1.991550995775496</v>
       </c>
       <c r="H66" s="0">
-        <v>0.75555303073339708</v>
+        <v>1.9882974492984134</v>
       </c>
       <c r="I66" s="0">
-        <v>0.55212408889594988</v>
+        <v>1.9026434430299282</v>
       </c>
       <c r="J66" s="0">
-        <v>0.64409274935590677</v>
+        <v>1.4538093485461894</v>
       </c>
       <c r="K66" s="0">
         <v>0</v>
       </c>
       <c r="L66" s="0">
-        <v>0.63757658694367503</v>
+        <v>2.0402450782197601</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="0">
-        <v>0.61041646155360785</v>
+        <v>2.1438416855370659</v>
       </c>
       <c r="B67" s="0">
-        <v>1.1403508771929816</v>
+        <v>3.7719298245614001</v>
       </c>
       <c r="C67" s="0">
-        <v>0.57063873495732842</v>
+        <v>1.8843759114368666</v>
       </c>
       <c r="D67" s="0">
-        <v>0.25244632510278148</v>
+        <v>1.7118265092683849</v>
       </c>
       <c r="E67" s="0">
-        <v>0.45049076643097907</v>
+        <v>2.0454070825501933</v>
       </c>
       <c r="F67" s="0">
-        <v>0.63493796164901883</v>
+        <v>1.9102718043881657</v>
       </c>
       <c r="G67" s="0">
-        <v>0.78455039227519552</v>
+        <v>2.0116676725005012</v>
       </c>
       <c r="H67" s="0">
-        <v>0.70442538203715221</v>
+        <v>1.9542123501675834</v>
       </c>
       <c r="I67" s="0">
-        <v>0.47466783182061878</v>
+        <v>1.8807968064189375</v>
       </c>
       <c r="J67" s="0">
-        <v>0.80971659919028272</v>
+        <v>1.6194331983805654</v>
       </c>
       <c r="K67" s="0">
         <v>0</v>
       </c>
       <c r="L67" s="0">
-        <v>0.60492022517338928</v>
+        <v>1.8785183342145351</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="0">
-        <v>0.54395983065865861</v>
+        <v>2.0256965639460449</v>
       </c>
       <c r="B68" s="0">
-        <v>1.2280701754385954</v>
+        <v>2.0175438596491211</v>
       </c>
       <c r="C68" s="0">
-        <v>0.55668978810281589</v>
+        <v>1.8095588328535723</v>
       </c>
       <c r="D68" s="0">
-        <v>0.27648883225542736</v>
+        <v>1.7575072728584122</v>
       </c>
       <c r="E68" s="0">
-        <v>0.40275664548465012</v>
+        <v>2.0627107013932378</v>
       </c>
       <c r="F68" s="0">
-        <v>0.62038350980606138</v>
+        <v>1.7901975766837666</v>
       </c>
       <c r="G68" s="0">
-        <v>0.6638503319251654</v>
+        <v>2.2329511164755562</v>
       </c>
       <c r="H68" s="0">
-        <v>0.71010623189229038</v>
+        <v>2.0053399988638283</v>
       </c>
       <c r="I68" s="0">
-        <v>0.47665388969434525</v>
+        <v>1.7159540028996429</v>
       </c>
       <c r="J68" s="0">
-        <v>0.53367684946632266</v>
+        <v>1.9506808980493173</v>
       </c>
       <c r="K68" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L68" s="0">
-        <v>0.62202593848163412</v>
+        <v>1.7494479519795958</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="0">
-        <v>0.55134390075810347</v>
+        <v>2.0527714876440104</v>
       </c>
       <c r="B69" s="0">
-        <v>0.35087719298245973</v>
+        <v>1.9298245614035285</v>
       </c>
       <c r="C69" s="0">
-        <v>0.48694505383025893</v>
+        <v>1.6890906554737106</v>
       </c>
       <c r="D69" s="0">
-        <v>0.25965907724857812</v>
+        <v>1.5795927199288502</v>
       </c>
       <c r="E69" s="0">
-        <v>0.3317521405769896</v>
+        <v>1.9415853694919498</v>
       </c>
       <c r="F69" s="0">
-        <v>0.61674489684532885</v>
+        <v>1.7556307535567621</v>
       </c>
       <c r="G69" s="0">
-        <v>0.54315027157514129</v>
+        <v>2.0519010259505341</v>
       </c>
       <c r="H69" s="0">
-        <v>0.8975742771118651</v>
+        <v>1.9826165994432972</v>
       </c>
       <c r="I69" s="0">
-        <v>0.41508609560883031</v>
+        <v>1.4617385950626751</v>
       </c>
       <c r="J69" s="0">
-        <v>0.68089804931910891</v>
+        <v>1.7482517482517663</v>
       </c>
       <c r="K69" s="0">
-        <v>0</v>
+        <v>0.90206185567011221</v>
       </c>
       <c r="L69" s="0">
-        <v>0.61736074394302876</v>
+        <v>1.6810250987466349</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="0">
-        <v>0.47258048636408345</v>
+        <v>1.8534015949591396</v>
       </c>
       <c r="B70" s="0">
-        <v>0.52631578947368374</v>
+        <v>1.4035087719298234</v>
       </c>
       <c r="C70" s="0">
-        <v>0.45397481581049681</v>
+        <v>1.6218820933564957</v>
       </c>
       <c r="D70" s="0">
-        <v>0.29572283797754406</v>
+        <v>1.3439761498329035</v>
       </c>
       <c r="E70" s="0">
-        <v>0.29893493242638475</v>
+        <v>1.8646140994659728</v>
       </c>
       <c r="F70" s="0">
-        <v>0.54215333115016506</v>
+        <v>1.6592075100971495</v>
       </c>
       <c r="G70" s="0">
-        <v>0.54315027157513529</v>
+        <v>1.9513176423254861</v>
       </c>
       <c r="H70" s="0">
-        <v>0.57944668522410903</v>
+        <v>1.823552803499402</v>
       </c>
       <c r="I70" s="0">
-        <v>0.3614625330182118</v>
+        <v>1.5233063891481784</v>
       </c>
       <c r="J70" s="0">
-        <v>0.4600662495399333</v>
+        <v>1.8402649981597332</v>
       </c>
       <c r="K70" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L70" s="0">
-        <v>0.55982334463347072</v>
+        <v>1.6903554878238409</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="0">
-        <v>0.38889435857044369</v>
+        <v>1.8287880279610107</v>
       </c>
       <c r="B71" s="0">
-        <v>0.70175438596491169</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C71" s="0">
-        <v>0.37915773722720264</v>
+        <v>1.5204352071418594</v>
       </c>
       <c r="D71" s="0">
-        <v>0.26206332796383985</v>
+        <v>1.2165508619238805</v>
       </c>
       <c r="E71" s="0">
-        <v>0.27984128404785319</v>
+        <v>1.8150899489841565</v>
       </c>
       <c r="F71" s="0">
-        <v>0.53487610522868634</v>
+        <v>1.5791580249608836</v>
       </c>
       <c r="G71" s="0">
-        <v>0.46268356467511529</v>
+        <v>1.8105009052504511</v>
       </c>
       <c r="H71" s="0">
-        <v>0.54536158609327912</v>
+        <v>1.6758507072658055</v>
       </c>
       <c r="I71" s="0">
-        <v>0.35351830152330604</v>
+        <v>1.3386030068916197</v>
       </c>
       <c r="J71" s="0">
-        <v>0.57048214942951736</v>
+        <v>2.0426941479573042</v>
       </c>
       <c r="K71" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L71" s="0">
-        <v>0.49606568593910322</v>
+        <v>1.4804217335862893</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="0">
-        <v>0.38643300187063073</v>
+        <v>1.6786452692724214</v>
       </c>
       <c r="B72" s="0">
-        <v>0.52631578947368374</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C72" s="0">
-        <v>0.2967321421778108</v>
+        <v>1.4088436323057596</v>
       </c>
       <c r="D72" s="0">
-        <v>0.15146779506166888</v>
+        <v>0.91842377323107172</v>
       </c>
       <c r="E72" s="0">
-        <v>0.22375369193591677</v>
+        <v>1.6683075270741952</v>
       </c>
       <c r="F72" s="0">
-        <v>0.43845286176909321</v>
+        <v>1.6537495906560404</v>
       </c>
       <c r="G72" s="0">
-        <v>0.40233353450010018</v>
+        <v>1.2271172802253056</v>
       </c>
       <c r="H72" s="0">
-        <v>0.52263818667272577</v>
+        <v>1.6701698574106672</v>
       </c>
       <c r="I72" s="0">
-        <v>0.33167166491231526</v>
+        <v>1.3346308911441669</v>
       </c>
       <c r="J72" s="0">
-        <v>0.58888479941111471</v>
+        <v>1.2513801987486188</v>
       </c>
       <c r="K72" s="0">
-        <v>0</v>
+        <v>0.77319587628865916</v>
       </c>
       <c r="L72" s="0">
-        <v>0.47895997263085832</v>
+        <v>1.4695362796628606</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="0">
-        <v>0.31505365757605563</v>
+        <v>1.5555774342817748</v>
       </c>
       <c r="B73" s="0">
         <v>0.26315789473684187</v>
       </c>
       <c r="C73" s="0">
-        <v>0.24727678514817564</v>
+        <v>1.4126478905388085</v>
       </c>
       <c r="D73" s="0">
-        <v>0.16348904863799182</v>
+        <v>0.84870050248839868</v>
       </c>
       <c r="E73" s="0">
-        <v>0.1843730421551954</v>
+        <v>1.5871595214654362</v>
       </c>
       <c r="F73" s="0">
-        <v>0.45846523305315967</v>
+        <v>1.3863115380416973</v>
       </c>
       <c r="G73" s="0">
-        <v>0.26151679742506517</v>
+        <v>1.2271172802253056</v>
       </c>
       <c r="H73" s="0">
-        <v>0.48287223768675752</v>
+        <v>1.4940635119013792</v>
       </c>
       <c r="I73" s="0">
-        <v>0.30188079680641866</v>
+        <v>1.1598577982562401</v>
       </c>
       <c r="J73" s="0">
-        <v>0.44166359955833606</v>
+        <v>1.2881854987118135</v>
       </c>
       <c r="K73" s="0">
-        <v>0.25773195876288635</v>
+        <v>0.64432989690721587</v>
       </c>
       <c r="L73" s="0">
-        <v>0.40120673032065401</v>
+        <v>1.3933381021988605</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="0">
-        <v>0.30028551737717801</v>
+        <v>1.3955892487939339</v>
       </c>
       <c r="B74" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C74" s="0">
-        <v>0.19148099773012575</v>
+        <v>1.3035924878580747</v>
       </c>
       <c r="D74" s="0">
-        <v>0.1346380400548168</v>
+        <v>0.81023249104416539</v>
       </c>
       <c r="E74" s="0">
-        <v>0.17482621796592962</v>
+        <v>1.5048181628330188</v>
       </c>
       <c r="F74" s="0">
-        <v>0.41116326456354801</v>
+        <v>1.4317942000509392</v>
       </c>
       <c r="G74" s="0">
-        <v>0.22128344397505512</v>
+        <v>1.3679340173003409</v>
       </c>
       <c r="H74" s="0">
-        <v>0.3351701414531611</v>
+        <v>1.2441061182752928</v>
       </c>
       <c r="I74" s="0">
-        <v>0.22243848185736112</v>
+        <v>1.118150582907985</v>
       </c>
       <c r="J74" s="0">
-        <v>0.49687154950312801</v>
+        <v>1.324990798675008</v>
       </c>
       <c r="K74" s="0">
-        <v>0</v>
+        <v>0.90206185567010222</v>
       </c>
       <c r="L74" s="0">
-        <v>0.36233010916555186</v>
+        <v>1.2347214878860437</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="0">
-        <v>0.29536280397755216</v>
+        <v>1.3217485477995459</v>
       </c>
       <c r="B75" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C75" s="0">
-        <v>0.18133630910866214</v>
+        <v>1.1907328269442918</v>
       </c>
       <c r="D75" s="0">
-        <v>0.098574279325848016</v>
+        <v>0.72367946529464022</v>
       </c>
       <c r="E75" s="0">
-        <v>0.14976580446910695</v>
+        <v>1.3699692711596396</v>
       </c>
       <c r="F75" s="0">
-        <v>0.33657169886839106</v>
+        <v>1.3171778917876493</v>
       </c>
       <c r="G75" s="0">
-        <v>0.26151679742506517</v>
+        <v>1.2874673104003207</v>
       </c>
       <c r="H75" s="0">
-        <v>0.35789354087371439</v>
+        <v>1.2327444185650163</v>
       </c>
       <c r="I75" s="0">
-        <v>0.23435482909971977</v>
+        <v>1.0387082679589275</v>
       </c>
       <c r="J75" s="0">
-        <v>0.34965034965034936</v>
+        <v>1.10415899889584</v>
       </c>
       <c r="K75" s="0">
-        <v>0</v>
+        <v>0.25773195876288635</v>
       </c>
       <c r="L75" s="0">
-        <v>0.32034335831804162</v>
+        <v>1.2191708394240031</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="0">
-        <v>0.26336516687998401</v>
+        <v>1.3119031210002943</v>
       </c>
       <c r="B76" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.52631578947368374</v>
       </c>
       <c r="C76" s="0">
-        <v>0.12554052169061225</v>
+        <v>1.1717115357790475</v>
       </c>
       <c r="D76" s="0">
-        <v>0.086553025749525073</v>
+        <v>0.76214747673887362</v>
       </c>
       <c r="E76" s="0">
-        <v>0.12291536143679692</v>
+        <v>1.2792744413616148</v>
       </c>
       <c r="F76" s="0">
-        <v>0.32201724702543366</v>
+        <v>1.2116581159262079</v>
       </c>
       <c r="G76" s="0">
-        <v>0.24140012070006014</v>
+        <v>0.98571715952524564</v>
       </c>
       <c r="H76" s="0">
-        <v>0.26699994319150122</v>
+        <v>1.2441061182752928</v>
       </c>
       <c r="I76" s="0">
-        <v>0.20456396099382318</v>
+        <v>0.96919624237850211</v>
       </c>
       <c r="J76" s="0">
-        <v>0.20242914979757068</v>
+        <v>1.0121457489878534</v>
       </c>
       <c r="K76" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L76" s="0">
-        <v>0.31567816377942931</v>
+        <v>1.1445277268062069</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="0">
-        <v>0.21659938958353825</v>
+        <v>1.2651373437038485</v>
       </c>
       <c r="B77" s="0">
-        <v>0</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C77" s="0">
-        <v>0.11285966091378272</v>
+        <v>1.0905540268073388</v>
       </c>
       <c r="D77" s="0">
-        <v>0.081744524318995912</v>
+        <v>0.71646671314884647</v>
       </c>
       <c r="E77" s="0">
-        <v>0.096661594916316027</v>
+        <v>1.2040932008711467</v>
       </c>
       <c r="F77" s="0">
-        <v>0.27107666557508253</v>
+        <v>1.1334279372703115</v>
       </c>
       <c r="G77" s="0">
-        <v>0.22128344397505512</v>
+        <v>1.3075839871253259</v>
       </c>
       <c r="H77" s="0">
-        <v>0.27836164290177784</v>
+        <v>1.2554678179855696</v>
       </c>
       <c r="I77" s="0">
-        <v>0.16682886139302086</v>
+        <v>0.91358662191416184</v>
       </c>
       <c r="J77" s="0">
-        <v>0.331247699668752</v>
+        <v>1.0857563489142428</v>
       </c>
       <c r="K77" s="0">
         <v>0</v>
       </c>
       <c r="L77" s="0">
-        <v>0.27369141293191901</v>
+        <v>1.0978757814200844</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="0">
-        <v>0.18214039578615718</v>
+        <v>1.1937579994092733</v>
       </c>
       <c r="B78" s="0">
-        <v>0</v>
+        <v>0.17543859649122792</v>
       </c>
       <c r="C78" s="0">
-        <v>0.081157508971708925</v>
+        <v>0.98530288235965358</v>
       </c>
       <c r="D78" s="0">
-        <v>0.057702017166350053</v>
+        <v>0.69963695814199434</v>
       </c>
       <c r="E78" s="0">
-        <v>0.084131388167904692</v>
+        <v>1.0871446045526407</v>
       </c>
       <c r="F78" s="0">
-        <v>0.21649747116399209</v>
+        <v>1.1261507113488329</v>
       </c>
       <c r="G78" s="0">
-        <v>0.26151679742506517</v>
+        <v>1.3277006638503308</v>
       </c>
       <c r="H78" s="0">
-        <v>0.27836164290177784</v>
+        <v>1.2725103675509846</v>
       </c>
       <c r="I78" s="0">
-        <v>0.17675915076165302</v>
+        <v>0.87585152231335939</v>
       </c>
       <c r="J78" s="0">
-        <v>0.331247699668752</v>
+        <v>1.0305483989694506</v>
       </c>
       <c r="K78" s="0">
         <v>0</v>
       </c>
       <c r="L78" s="0">
-        <v>0.22859453239200053</v>
+        <v>1.1180916244207375</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="0">
-        <v>0.14522004528896315</v>
+        <v>1.1396081520133887</v>
       </c>
       <c r="B79" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.43859649122806976</v>
       </c>
       <c r="C79" s="0">
-        <v>0.057063873495732838</v>
+        <v>0.91936240632014021</v>
       </c>
       <c r="D79" s="0">
-        <v>0.067319020027408402</v>
+        <v>0.55297766451085473</v>
       </c>
       <c r="E79" s="0">
-        <v>0.061457680718398459</v>
+        <v>1.0155434231331475</v>
       </c>
       <c r="F79" s="0">
-        <v>0.18738856747807719</v>
+        <v>1.0824873558199604</v>
       </c>
       <c r="G79" s="0">
-        <v>0.34198350432508523</v>
+        <v>0.82478374572520541</v>
       </c>
       <c r="H79" s="0">
-        <v>0.20451059478497965</v>
+        <v>1.1418508208828031</v>
       </c>
       <c r="I79" s="0">
-        <v>0.10526106730750123</v>
+        <v>0.80435343885920763</v>
       </c>
       <c r="J79" s="0">
-        <v>0.18402649981597335</v>
+        <v>0.86492454913507477</v>
       </c>
       <c r="K79" s="0">
         <v>0</v>
       </c>
       <c r="L79" s="0">
-        <v>0.17261219792865345</v>
+        <v>0.97813578826236969</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="0">
-        <v>0.10583833809195618</v>
+        <v>0.93531554592891519</v>
       </c>
       <c r="B80" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C80" s="0">
-        <v>0.05199152918500103</v>
+        <v>0.91048580377635957</v>
       </c>
       <c r="D80" s="0">
-        <v>0.074531772173202157</v>
+        <v>0.52412665592767971</v>
       </c>
       <c r="E80" s="0">
-        <v>0.044154061875354242</v>
+        <v>0.92365524031146429</v>
       </c>
       <c r="F80" s="0">
-        <v>0.15464105083142293</v>
+        <v>0.9569552086744525</v>
       </c>
       <c r="G80" s="0">
-        <v>0.080466706900020044</v>
+        <v>1.0259505129752555</v>
       </c>
       <c r="H80" s="0">
-        <v>0.14202124637845809</v>
+        <v>1.0679997727660049</v>
       </c>
       <c r="I80" s="0">
-        <v>0.095330777938869057</v>
+        <v>0.80633949673293415</v>
       </c>
       <c r="J80" s="0">
-        <v>0.12881854987118133</v>
+        <v>1.2145748987854241</v>
       </c>
       <c r="K80" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L80" s="0">
-        <v>0.13995583615836768</v>
+        <v>0.94236929679967574</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="0">
-        <v>0.08614748449345272</v>
+        <v>0.92793147582947644</v>
       </c>
       <c r="B81" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C81" s="0">
-        <v>0.03931066840817151</v>
+        <v>0.86229853282440727</v>
       </c>
       <c r="D81" s="0">
-        <v>0.057702017166350053</v>
+        <v>0.38227586372706912</v>
       </c>
       <c r="E81" s="0">
-        <v>0.031027178615113789</v>
+        <v>0.84907067633282551</v>
       </c>
       <c r="F81" s="0">
-        <v>0.12371284066513834</v>
+        <v>1.0370046938107185</v>
       </c>
       <c r="G81" s="0">
-        <v>0.060350030175015036</v>
+        <v>0.82478374572520541</v>
       </c>
       <c r="H81" s="0">
-        <v>0.15906379594387307</v>
+        <v>0.94302107595296181</v>
       </c>
       <c r="I81" s="0">
-        <v>0.075470199201604665</v>
+        <v>0.66532938769835692</v>
       </c>
       <c r="J81" s="0">
-        <v>0.12881854987118133</v>
+        <v>1.0857563489142428</v>
       </c>
       <c r="K81" s="0">
-        <v>0.25773195876288635</v>
+        <v>0</v>
       </c>
       <c r="L81" s="0">
-        <v>0.11818492831151048</v>
+        <v>0.94547942649208383</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="0">
-        <v>0.068917987594762933</v>
+        <v>0.83932263463622003</v>
       </c>
       <c r="B82" s="0">
-        <v>0.17543859649122986</v>
+        <v>0.87719298245614929</v>
       </c>
       <c r="C82" s="0">
-        <v>0.032970238019757118</v>
+        <v>0.78240910993039003</v>
       </c>
       <c r="D82" s="0">
-        <v>0.057702017166350691</v>
+        <v>0.3317865987065165</v>
       </c>
       <c r="E82" s="0">
-        <v>0.026850443032310305</v>
+        <v>0.77806617142516976</v>
       </c>
       <c r="F82" s="0">
-        <v>0.078230178655897167</v>
+        <v>0.83142306152895373</v>
       </c>
       <c r="G82" s="0">
-        <v>0.10058338362502617</v>
+        <v>0.70408368537518318</v>
       </c>
       <c r="H82" s="0">
-        <v>0.11361699710276772</v>
+        <v>1.0225529739249097</v>
       </c>
       <c r="I82" s="0">
-        <v>0.049651446843161515</v>
+        <v>0.64745486683482611</v>
       </c>
       <c r="J82" s="0">
-        <v>0.09201324990798769</v>
+        <v>0.99374309900626701</v>
       </c>
       <c r="K82" s="0">
-        <v>0.25773195876288924</v>
+        <v>0</v>
       </c>
       <c r="L82" s="0">
-        <v>0.063757658694368211</v>
+        <v>0.77131216371723488</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="0">
-        <v>0.044304420596632824</v>
+        <v>0.85409077483508822</v>
       </c>
       <c r="B83" s="0">
-        <v>0</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C83" s="0">
-        <v>0.01268086077682952</v>
+        <v>0.74436652759989286</v>
       </c>
       <c r="D83" s="0">
-        <v>0.031255259298439614</v>
+        <v>0.32938234799124821</v>
       </c>
       <c r="E83" s="0">
-        <v>0.007160118141949336</v>
+        <v>0.713028431635788</v>
       </c>
       <c r="F83" s="0">
-        <v>0.065495033293308524</v>
+        <v>0.75501218935341785</v>
       </c>
       <c r="G83" s="0">
-        <v>0.060350030175015036</v>
+        <v>0.90525045262522552</v>
       </c>
       <c r="H83" s="0">
-        <v>0.079531897971936535</v>
+        <v>0.77259558029881203</v>
       </c>
       <c r="I83" s="0">
-        <v>0.045679331095708091</v>
+        <v>0.6454688089610926</v>
       </c>
       <c r="J83" s="0">
-        <v>0.11041589988958402</v>
+        <v>0.97534044902465866</v>
       </c>
       <c r="K83" s="0">
-        <v>0.77319587628865916</v>
+        <v>0</v>
       </c>
       <c r="L83" s="0">
-        <v>0.068422853232979752</v>
+        <v>0.79774826610269578</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="0">
-        <v>0.044304420596632824</v>
+        <v>0.70394801614649927</v>
       </c>
       <c r="B84" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.87719298245613953</v>
       </c>
       <c r="C84" s="0">
-        <v>0.0088766025437806654</v>
+        <v>0.62643452237537822</v>
       </c>
       <c r="D84" s="0">
-        <v>0.016829755006852101</v>
+        <v>0.3005313394080732</v>
       </c>
       <c r="E84" s="0">
-        <v>0.0095468241892657808</v>
+        <v>0.65336078045287693</v>
       </c>
       <c r="F84" s="0">
-        <v>0.040024742568132987</v>
+        <v>0.7823017865589631</v>
       </c>
       <c r="G84" s="0">
-        <v>0.040233353450010022</v>
+        <v>0.66385033192516541</v>
       </c>
       <c r="H84" s="0">
-        <v>0.079531897971936535</v>
+        <v>0.73851048116798212</v>
       </c>
       <c r="I84" s="0">
-        <v>0.037735099600802333</v>
+        <v>0.52829139441123263</v>
       </c>
       <c r="J84" s="0">
-        <v>0.165623849834376</v>
+        <v>0.93853514906146396</v>
       </c>
       <c r="K84" s="0">
-        <v>0.90206185567010222</v>
+        <v>0</v>
       </c>
       <c r="L84" s="0">
-        <v>0.037321556308898045</v>
+        <v>0.70910956986906293</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="0">
-        <v>0.03692035049719402</v>
+        <v>0.66210495224967947</v>
       </c>
       <c r="B85" s="0">
-        <v>0.26315789473684187</v>
+        <v>1.3157894736842093</v>
       </c>
       <c r="C85" s="0">
-        <v>0.0088766025437806654</v>
+        <v>0.67842605156037938</v>
       </c>
       <c r="D85" s="0">
-        <v>0.024042507152645855</v>
+        <v>0.25725482653331067</v>
       </c>
       <c r="E85" s="0">
-        <v>0.0029833825591455568</v>
+        <v>0.5745994808914342</v>
       </c>
       <c r="F85" s="0">
-        <v>0.041844049048502675</v>
+        <v>0.76047010879452681</v>
       </c>
       <c r="G85" s="0">
-        <v>0.040233353450010022</v>
+        <v>0.68396700865017046</v>
       </c>
       <c r="H85" s="0">
-        <v>0.079531897971936535</v>
+        <v>0.67034028290632219</v>
       </c>
       <c r="I85" s="0">
-        <v>0.029790868105896578</v>
+        <v>0.50445869992651538</v>
       </c>
       <c r="J85" s="0">
-        <v>0.073610599926389339</v>
+        <v>0.66249539933750401</v>
       </c>
       <c r="K85" s="0">
-        <v>0.90206185567010222</v>
+        <v>0</v>
       </c>
       <c r="L85" s="0">
-        <v>0.057537399309551158</v>
+        <v>0.75731658010138958</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="0">
-        <v>0.017229496898690543</v>
+        <v>0.5390371172590327</v>
       </c>
       <c r="B86" s="0">
-        <v>0.35087719298245584</v>
+        <v>1.1403508771929816</v>
       </c>
       <c r="C86" s="0">
-        <v>0.0076085164660977117</v>
+        <v>0.58966002612257273</v>
       </c>
       <c r="D86" s="0">
-        <v>0.0072127521457937566</v>
+        <v>0.23080806866540021</v>
       </c>
       <c r="E86" s="0">
-        <v>0.0029833825591455568</v>
+        <v>0.4827112980697511</v>
       </c>
       <c r="F86" s="0">
-        <v>0.016373758323327131</v>
+        <v>0.70771022086380608</v>
       </c>
       <c r="G86" s="0">
-        <v>0.060350030175015036</v>
+        <v>0.74431703882518541</v>
       </c>
       <c r="H86" s="0">
-        <v>0.073851048116798199</v>
+        <v>0.68738283247173715</v>
       </c>
       <c r="I86" s="0">
-        <v>0.025818752358443702</v>
+        <v>0.47466783182061878</v>
       </c>
       <c r="J86" s="0">
-        <v>0.073610599926389339</v>
+        <v>0.55207949944792001</v>
       </c>
       <c r="K86" s="0">
-        <v>2.0618556701030908</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L86" s="0">
-        <v>0.024881037539265367</v>
+        <v>0.66556775417534852</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="0">
-        <v>0.017229496898690543</v>
+        <v>0.62518460175248536</v>
       </c>
       <c r="B87" s="0">
-        <v>0.17543859649122792</v>
+        <v>0.70175438596491169</v>
       </c>
       <c r="C87" s="0">
-        <v>0.0025361721553659039</v>
+        <v>0.55161744379208411</v>
       </c>
       <c r="D87" s="0">
-        <v>0.012021253576322928</v>
+        <v>0.27889308297069193</v>
       </c>
       <c r="E87" s="0">
-        <v>0.0011933530236582226</v>
+        <v>0.44154061875354234</v>
       </c>
       <c r="F87" s="0">
-        <v>0.0018193064803696812</v>
+        <v>0.62584142924717034</v>
       </c>
       <c r="G87" s="0">
-        <v>0.040233353450010022</v>
+        <v>0.72420036210018035</v>
       </c>
       <c r="H87" s="0">
-        <v>0.068170198261659889</v>
+        <v>0.65897858319604552</v>
       </c>
       <c r="I87" s="0">
-        <v>0.0099302893686321926</v>
+        <v>0.4230303271037314</v>
       </c>
       <c r="J87" s="0">
-        <v>0.03680529996319467</v>
+        <v>0.55207949944792001</v>
       </c>
       <c r="K87" s="0">
-        <v>1.417525773195875</v>
+        <v>0</v>
       </c>
       <c r="L87" s="0">
-        <v>0.0062202593848163417</v>
+        <v>0.63757658694367503</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.59564832135473023</v>
       </c>
       <c r="B88" s="0">
-        <v>0.087719298245613961</v>
+        <v>1.0526315789473675</v>
       </c>
       <c r="C88" s="0">
-        <v>0.0025361721553659039</v>
+        <v>0.37915773722720264</v>
       </c>
       <c r="D88" s="0">
-        <v>0</v>
+        <v>0.26446757867910442</v>
       </c>
       <c r="E88" s="0">
-        <v>0.0011933530236582226</v>
+        <v>0.42960708851696011</v>
       </c>
       <c r="F88" s="0">
-        <v>0.0036386129607393625</v>
+        <v>0.59491321908088579</v>
       </c>
       <c r="G88" s="0">
-        <v>0</v>
+        <v>0.56326694830014024</v>
       </c>
       <c r="H88" s="0">
-        <v>0.017042549565414972</v>
+        <v>0.70442538203715222</v>
       </c>
       <c r="I88" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0.42104426923000493</v>
       </c>
       <c r="J88" s="0">
-        <v>0.018402649981597335</v>
+        <v>0.62569009937430942</v>
       </c>
       <c r="K88" s="0">
-        <v>1.0309278350515454</v>
+        <v>0</v>
       </c>
       <c r="L88" s="0">
-        <v>0.0062202593848163417</v>
+        <v>0.58625944701894017</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.49227133996258693</v>
       </c>
       <c r="B89" s="0">
-        <v>0.26315789473684187</v>
+        <v>0.61403508771929771</v>
       </c>
       <c r="C89" s="0">
-        <v>0</v>
+        <v>0.37408539291647086</v>
       </c>
       <c r="D89" s="0">
-        <v>0</v>
+        <v>0.24763782367225232</v>
       </c>
       <c r="E89" s="0">
-        <v>0</v>
+        <v>0.36337599570392876</v>
       </c>
       <c r="F89" s="0">
-        <v>0</v>
+        <v>0.54943055707164379</v>
       </c>
       <c r="G89" s="0">
-        <v>0.060350030175015036</v>
+        <v>0.40233353450010018</v>
       </c>
       <c r="H89" s="0">
-        <v>0.005680849855138323</v>
+        <v>0.64193603363063056</v>
       </c>
       <c r="I89" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0.35153224364957964</v>
       </c>
       <c r="J89" s="0">
-        <v>0</v>
+        <v>0.73610599926389342</v>
       </c>
       <c r="K89" s="0">
-        <v>1.1597938144329887</v>
+        <v>0</v>
       </c>
       <c r="L89" s="0">
-        <v>0.0031101296924081708</v>
+        <v>0.54427269617142993</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="0">
-        <v>0.0024613566998129346</v>
+        <v>0.44058284926651536</v>
       </c>
       <c r="B90" s="0">
-        <v>0.087719298245613961</v>
+        <v>0.35087719298245584</v>
       </c>
       <c r="C90" s="0">
-        <v>0</v>
+        <v>0.36520879037269016</v>
       </c>
       <c r="D90" s="0">
-        <v>0</v>
+        <v>0.16589329935325642</v>
       </c>
       <c r="E90" s="0">
-        <v>0</v>
+        <v>0.31504519824577076</v>
       </c>
       <c r="F90" s="0">
-        <v>0</v>
+        <v>0.51486373394461982</v>
       </c>
       <c r="G90" s="0">
-        <v>0</v>
+        <v>0.48280024140012029</v>
       </c>
       <c r="H90" s="0">
-        <v>0</v>
+        <v>0.61353178435493894</v>
       </c>
       <c r="I90" s="0">
-        <v>0</v>
+        <v>0.32174137554368304</v>
       </c>
       <c r="J90" s="0">
-        <v>0.018402649981597335</v>
+        <v>0.49687154950312801</v>
       </c>
       <c r="K90" s="0">
-        <v>0.38659793814432958</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L90" s="0">
-        <v>0</v>
+        <v>0.49451062109289917</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="0">
-        <v>0</v>
+        <v>0.44304420596632821</v>
       </c>
       <c r="B91" s="0">
         <v>0.17543859649122792</v>
       </c>
       <c r="C91" s="0">
-        <v>0</v>
+        <v>0.27263850670183471</v>
       </c>
       <c r="D91" s="0">
-        <v>0</v>
+        <v>0.14425504291587515</v>
       </c>
       <c r="E91" s="0">
-        <v>0</v>
+        <v>0.28998478474894812</v>
       </c>
       <c r="F91" s="0">
-        <v>0</v>
+        <v>0.44391078121020228</v>
       </c>
       <c r="G91" s="0">
-        <v>0.020116676725005011</v>
+        <v>0.30175015087507517</v>
       </c>
       <c r="H91" s="0">
-        <v>0</v>
+        <v>0.46582968812134257</v>
       </c>
       <c r="I91" s="0">
-        <v>0</v>
+        <v>0.28599233381660716</v>
       </c>
       <c r="J91" s="0">
-        <v>0</v>
+        <v>0.60728744939271206</v>
       </c>
       <c r="K91" s="0">
-        <v>0.38659793814432958</v>
+        <v>0</v>
       </c>
       <c r="L91" s="0">
-        <v>0.0015550648462040854</v>
+        <v>0.47740490778465416</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="0">
-        <v>0</v>
+        <v>0.43566013586688945</v>
       </c>
       <c r="B92" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C92" s="0">
-        <v>0</v>
+        <v>0.22952358006061432</v>
       </c>
       <c r="D92" s="0">
-        <v>0</v>
+        <v>0.1178082850479647</v>
       </c>
       <c r="E92" s="0">
-        <v>0</v>
+        <v>0.2428473403144483</v>
       </c>
       <c r="F92" s="0">
-        <v>0</v>
+        <v>0.42389840992613581</v>
       </c>
       <c r="G92" s="0">
-        <v>0</v>
+        <v>0.28163347415007012</v>
       </c>
       <c r="H92" s="0">
-        <v>0</v>
+        <v>0.45446798841106584</v>
       </c>
       <c r="I92" s="0">
-        <v>0.0019860578737264387</v>
+        <v>0.27407598657424853</v>
       </c>
       <c r="J92" s="0">
-        <v>0</v>
+        <v>0.331247699668752</v>
       </c>
       <c r="K92" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L92" s="0">
-        <v>0.0015550648462040854</v>
+        <v>0.38876621155102137</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="0">
-        <v>0</v>
+        <v>0.40366249876932126</v>
       </c>
       <c r="B93" s="0">
         <v>0</v>
       </c>
       <c r="C93" s="0">
-        <v>0</v>
+        <v>0.21557463320610182</v>
       </c>
       <c r="D93" s="0">
-        <v>0</v>
+        <v>0.11059553290217093</v>
       </c>
       <c r="E93" s="0">
-        <v>0</v>
+        <v>0.20287001402189783</v>
       </c>
       <c r="F93" s="0">
-        <v>0</v>
+        <v>0.34566823127023949</v>
       </c>
       <c r="G93" s="0">
-        <v>0</v>
+        <v>0.26151679742506517</v>
       </c>
       <c r="H93" s="0">
-        <v>0.005680849855138323</v>
+        <v>0.36925524058399106</v>
       </c>
       <c r="I93" s="0">
-        <v>0</v>
+        <v>0.21846636610990822</v>
       </c>
       <c r="J93" s="0">
-        <v>0</v>
+        <v>0.42326094957673871</v>
       </c>
       <c r="K93" s="0">
-        <v>0.12886597938144317</v>
+        <v>0</v>
       </c>
       <c r="L93" s="0">
-        <v>0</v>
+        <v>0.40898205455167447</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="0">
-        <v>0</v>
+        <v>0.29044009057792952</v>
       </c>
       <c r="B94" s="0">
-        <v>0</v>
+        <v>0.087719298245614932</v>
       </c>
       <c r="C94" s="0">
-        <v>0</v>
+        <v>0.15724267363268779</v>
       </c>
       <c r="D94" s="0">
-        <v>0</v>
+        <v>0.088957276464790652</v>
       </c>
       <c r="E94" s="0">
-        <v>0</v>
+        <v>0.17661624750141891</v>
       </c>
       <c r="F94" s="0">
-        <v>0</v>
+        <v>0.35476476367209181</v>
       </c>
       <c r="G94" s="0">
-        <v>0</v>
+        <v>0.26151679742506806</v>
       </c>
       <c r="H94" s="0">
-        <v>0</v>
+        <v>0.29540419246719607</v>
       </c>
       <c r="I94" s="0">
-        <v>0</v>
+        <v>0.19264761375146669</v>
       </c>
       <c r="J94" s="0">
-        <v>0</v>
+        <v>0.22083179977917047</v>
       </c>
       <c r="K94" s="0">
         <v>0</v>
       </c>
       <c r="L94" s="0">
-        <v>0</v>
+        <v>0.35921997947314771</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="0">
-        <v>0</v>
+        <v>0.27567195037904868</v>
       </c>
       <c r="B95" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C95" s="0">
-        <v>0</v>
+        <v>0.14329372677817359</v>
       </c>
       <c r="D95" s="0">
-        <v>0</v>
+        <v>0.088957276464789667</v>
       </c>
       <c r="E95" s="0">
-        <v>0</v>
+        <v>0.14260568632715759</v>
       </c>
       <c r="F95" s="0">
-        <v>0</v>
+        <v>0.31655932758432454</v>
       </c>
       <c r="G95" s="0">
-        <v>0</v>
+        <v>0.24140012070006015</v>
       </c>
       <c r="H95" s="0">
-        <v>0</v>
+        <v>0.29540419246719279</v>
       </c>
       <c r="I95" s="0">
-        <v>0</v>
+        <v>0.20456396099382318</v>
       </c>
       <c r="J95" s="0">
-        <v>0</v>
+        <v>0.36805299963194671</v>
       </c>
       <c r="K95" s="0">
         <v>0</v>
       </c>
       <c r="L95" s="0">
-        <v>0</v>
+        <v>0.30790283954840891</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="0">
-        <v>0</v>
+        <v>0.19198582258540892</v>
       </c>
       <c r="B96" s="0">
         <v>0</v>
       </c>
       <c r="C96" s="0">
-        <v>0</v>
+        <v>0.10017880013695321</v>
       </c>
       <c r="D96" s="0">
-        <v>0</v>
+        <v>0.098574279325848016</v>
       </c>
       <c r="E96" s="0">
-        <v>0</v>
+        <v>0.12589874399594248</v>
       </c>
       <c r="F96" s="0">
-        <v>0</v>
+        <v>0.2619801331732341</v>
       </c>
       <c r="G96" s="0">
-        <v>0</v>
+        <v>0.28163347415007012</v>
       </c>
       <c r="H96" s="0">
-        <v>0</v>
+        <v>0.29540419246719279</v>
       </c>
       <c r="I96" s="0">
-        <v>0</v>
+        <v>0.15689857202438864</v>
       </c>
       <c r="J96" s="0">
-        <v>0</v>
+        <v>0.23923444976076533</v>
       </c>
       <c r="K96" s="0">
         <v>0</v>
       </c>
       <c r="L96" s="0">
-        <v>0</v>
+        <v>0.24570024570024548</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="0">
-        <v>0</v>
+        <v>0.18706310918578303</v>
       </c>
       <c r="B97" s="0">
         <v>0</v>
       </c>
       <c r="C97" s="0">
-        <v>0</v>
+        <v>0.065940476039513501</v>
       </c>
       <c r="D97" s="0">
-        <v>0</v>
+        <v>0.050489265020556291</v>
       </c>
       <c r="E97" s="0">
-        <v>0</v>
+        <v>0.094871565380828693</v>
       </c>
       <c r="F97" s="0">
-        <v>0</v>
+        <v>0.22195539060510114</v>
       </c>
       <c r="G97" s="0">
-        <v>0</v>
+        <v>0.20116676725005009</v>
       </c>
       <c r="H97" s="0">
-        <v>0</v>
+        <v>0.18178719536442634</v>
       </c>
       <c r="I97" s="0">
-        <v>0</v>
+        <v>0.11320529880240701</v>
       </c>
       <c r="J97" s="0">
-        <v>0</v>
+        <v>0.18402649981597335</v>
       </c>
       <c r="K97" s="0">
         <v>0</v>
       </c>
       <c r="L97" s="0">
-        <v>0</v>
+        <v>0.20993375423755151</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="0">
-        <v>0</v>
+        <v>0.1772176823865313</v>
       </c>
       <c r="B98" s="0">
-        <v>0</v>
+        <v>0.087719298245613961</v>
       </c>
       <c r="C98" s="0">
-        <v>0</v>
+        <v>0.065940476039513501</v>
       </c>
       <c r="D98" s="0">
-        <v>0</v>
+        <v>0.081744524318995912</v>
       </c>
       <c r="E98" s="0">
-        <v>0</v>
+        <v>0.10382171305826537</v>
       </c>
       <c r="F98" s="0">
-        <v>0</v>
+        <v>0.21467816468362241</v>
       </c>
       <c r="G98" s="0">
-        <v>0</v>
+        <v>0.20116676725005009</v>
       </c>
       <c r="H98" s="0">
-        <v>0</v>
+        <v>0.22155314435039461</v>
       </c>
       <c r="I98" s="0">
-        <v>0</v>
+        <v>0.10923318305495411</v>
       </c>
       <c r="J98" s="0">
-        <v>0</v>
+        <v>0.14722119985277868</v>
       </c>
       <c r="K98" s="0">
         <v>0</v>
       </c>
       <c r="L98" s="0">
-        <v>0</v>
+        <v>0.22081920816098011</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="0">
-        <v>0</v>
+        <v>0.12060647829083379</v>
       </c>
       <c r="B99" s="0">
-        <v>0</v>
+        <v>0.26315789473684187</v>
       </c>
       <c r="C99" s="0">
-        <v>0</v>
+        <v>0.04565109879658627</v>
       </c>
       <c r="D99" s="0">
-        <v>0</v>
+        <v>0.062510518596879228</v>
       </c>
       <c r="E99" s="0">
-        <v>0</v>
+        <v>0.058474298159252917</v>
       </c>
       <c r="F99" s="0">
-        <v>0</v>
+        <v>0.12371284066513834</v>
       </c>
       <c r="G99" s="0">
-        <v>0</v>
+        <v>0.22128344397505512</v>
       </c>
       <c r="H99" s="0">
-        <v>0</v>
+        <v>0.22723399420553292</v>
       </c>
       <c r="I99" s="0">
-        <v>0</v>
+        <v>0.067525967706698914</v>
       </c>
       <c r="J99" s="0">
-        <v>0</v>
+        <v>0.23923444976076533</v>
       </c>
       <c r="K99" s="0">
-        <v>0</v>
+        <v>0.12886597938144317</v>
       </c>
       <c r="L99" s="0">
-        <v>0</v>
+        <v>0.16328180885142896</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="0">
-        <v>0</v>
+        <v>0.45288963276557997</v>
       </c>
       <c r="B100" s="0">
-        <v>0</v>
+        <v>1.7543859649122791</v>
       </c>
       <c r="C100" s="0">
-        <v>0</v>
+        <v>0.067208562117196446</v>
       </c>
       <c r="D100" s="0">
-        <v>0</v>
+        <v>0.14665929363113972</v>
       </c>
       <c r="E100" s="0">
-        <v>0</v>
+        <v>0.13365553864972093</v>
       </c>
       <c r="F100" s="0">
-        <v>0</v>
+        <v>0.36749990903467566</v>
       </c>
       <c r="G100" s="0">
-        <v>0</v>
+        <v>0.48280024140012029</v>
       </c>
       <c r="H100" s="0">
-        <v>0</v>
+        <v>0.56808498551383235</v>
       </c>
       <c r="I100" s="0">
-        <v>0</v>
+        <v>0.26017358145816344</v>
       </c>
       <c r="J100" s="0">
-        <v>0</v>
+        <v>0.64409274935590677</v>
       </c>
       <c r="K100" s="0">
-        <v>0</v>
+        <v>9.7938144329896826</v>
       </c>
       <c r="L100" s="0">
-        <v>0</v>
+        <v>0.41209218424408256</v>
       </c>
     </row>
   </sheetData>

--- a/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0004_ses-01_WMprob_pdf.xlsx
+++ b/braph2individualconnectome/pipelines/neuroimaging conversion structural/Example data NIfTI/reference_data/pdf_wmprob/sub-0004_ses-01_WMprob_pdf.xlsx
@@ -1,7 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fileVersion appName="libxl" rupBuild="4.6.0"/>
   <workbookPr/>
   <bookViews>
     <workbookView activeTab="0"/>
